--- a/data/grammar.xlsx
+++ b/data/grammar.xlsx
@@ -532,12 +532,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>他是第一名。</t>
+          <t>他得了第一。</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>He is first place.</t>
+          <t>He got first place.</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>桌子上有几本书？</t>
+          <t>书放在桌子上，包放在椅子下面。</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>How many books are on the table?</t>
+          <t>The book is on the table; the bag is under the chair.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>书店里的人很多。</t>
+          <t>学校外面有一家咖啡店，里面人很多。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>There are many people in the bookstore.</t>
+          <t>Outside the school there's a coffee shop; inside there are many people.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>他们都在国外。</t>
+          <t>前面是公园，后面是图书馆。</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>They are all abroad.</t>
+          <t>Ahead is a park; behind is a library.</t>
         </is>
       </c>
     </row>
@@ -879,32 +879,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>他去医院看病了。</t>
+          <t>上课的时候不能说话，下课再说。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>He went to the hospital to see a doctor.</t>
+          <t>You can't talk during class; talk after class.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>我想睡一觉，休息一下（儿）。</t>
+          <t>妈妈快要下班了，我们去接她吧。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I want to take a nap and rest for a bit.</t>
+          <t>Mom is about to finish work; let's go pick her up.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>上课不要说话。</t>
+          <t>他今天生病了，还是去上班了，没去看病。</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Don't talk during class.</t>
+          <t>He was sick today but still went to work instead of seeing a doctor.</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>你弟弟多大？</t>
+          <t>你叫什么名字？</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>How old is your younger brother?</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>这件衣服多少钱？</t>
+          <t>这是谁的书？</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>How much does this piece of clothing cost?</t>
+          <t>Whose book is this?</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>现在几点？</t>
+          <t>你最近怎么样？</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>What time is it now?</t>
+          <t>How have you been lately?</t>
         </is>
       </c>
     </row>
@@ -1003,32 +1003,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>我是学生。</t>
+          <t>我是学生，她是我同学。</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>I am a student.</t>
+          <t>I am a student and she is my classmate.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>你是哪国人？</t>
+          <t>我们班有二十人，他们都很努力，我们互相帮助。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>What country are you from?</t>
+          <t>Our class has 20 students; they all work hard and we help each other.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>老师，您好！</t>
+          <t>大家都喜欢这只猫，它很可爱。</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Hello, teacher!</t>
+          <t>Everyone likes this cat — it is very cute.</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>这是谁的书？</t>
+          <t>这本书是我的，那本是你的，这些都很有趣。</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Whose book is this?</t>
+          <t>This book is mine; that one is yours; these are all very interesting.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>那个手机多少钱？</t>
+          <t>那里有一家书店，这儿也有，那个书店更大。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>How much is that phone?</t>
+          <t>There's a bookstore there; there's one here too. That bookstore is bigger.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>我在这儿学习中文。</t>
+          <t>那些苹果，有些是红的，有的是绿的。</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>I study Chinese here.</t>
+          <t>Of those apples, some are red and some are green.</t>
         </is>
       </c>
     </row>
@@ -1122,32 +1122,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>一个、两百、五十八、一百零六、两千三百五十、九点半、半个小时</t>
+          <t>我买了两个苹果，他买了三个。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>one (item), two hundred, fifty-eight, one hundred and six, two thousand three hundred and fifty, nine thirty, half an hour</t>
+          <t>I bought two apples; he bought three.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>我买了两个苹果。</t>
+          <t>这栋楼有一百零一个房间。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>I bought two apples.</t>
+          <t>This building has 101 rooms.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>他家有三口人。</t>
+          <t>半小时后，他们就回来了。</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>There are three people in his family.</t>
+          <t>They'll be back in half an hour.</t>
         </is>
       </c>
     </row>
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>这本书是中文书。</t>
+          <t>我想买一件衬衫，多少钱一件？</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>This book is a Chinese book.</t>
+          <t>I want to buy a shirt. How much per item?</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>我吃了两个包子。</t>
+          <t>桌上有一只猫和两块蛋糕。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>I ate two steamed buns.</t>
+          <t>On the table there's a cat and two pieces of cake.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>前边有一家书店。</t>
+          <t>这本书二十元，那家书店有好几本。</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>There is a bookstore ahead.</t>
+          <t>This book is 20 yuan; that bookstore has several copies.</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>今天几月几日（号）？</t>
+          <t>今天几月几日？</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>What is today's date (month and day)?</t>
+          <t>What's today's date?</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1370,32 +1370,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>我非常喜欢学中文。</t>
+          <t>这部电影非常好看，你一定要看看。</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>I like learning Chinese very much.</t>
+          <t>This movie is extremely good; you must watch it.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>这里的水果很便宜。</t>
+          <t>今天很冷，有点儿风，多穿点儿衣服吧。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>The fruit here is very cheap.</t>
+          <t>Today is very cold with a slight breeze; put on more clothes.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>房间里太热了。</t>
+          <t>那道题真难，太难了，我做不出来。</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>It's too hot in the room.</t>
+          <t>That problem is really hard — too hard; I can't solve it.</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>请再写一次。</t>
+          <t>请再写一遍。</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>她去超市了，我没有去。</t>
+          <t>不要在图书馆里大声说话。</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>She went to the supermarket; I didn't go.</t>
+          <t>Don't talk loudly in the library.</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>他和朋友学习。</t>
+          <t>他和同学们一起去图书馆了。</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>He studies with his friend.</t>
+          <t>He went to the library together with his classmates.</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>我们走吧。</t>
+          <t>你是王老师吧？</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Let's go.</t>
+          <t>You're Teacher Wang, right?</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>八点了，起床吧。</t>
+          <t>他走了吗？</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>It's eight o'clock — time to get up.</t>
+          <t>Has he left?</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>她病了，在家休息呢。</t>
+          <t>你呢？</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>She's sick and is resting at home.</t>
+          <t>What about you?</t>
         </is>
       </c>
     </row>
@@ -2171,32 +2171,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>哥哥姐姐、今天和明天、有没有</t>
+          <t>爸爸和妈妈都很忙。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>older brother and older sister / today and tomorrow / have or not have</t>
+          <t>Dad and Mom are both very busy.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>爸爸妈妈都很好。</t>
+          <t>这家饭店又便宜又好吃。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Both mom and dad are doing well.</t>
+          <t>This restaurant is both cheap and delicious.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>他们来了又去了。</t>
+          <t>今天和明天都不上课。</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>They came and then left.</t>
+          <t>There are no classes today or tomorrow.</t>
         </is>
       </c>
     </row>
@@ -2233,32 +2233,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>好朋友、我的书、很喜欢</t>
+          <t>他是我的好朋友。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>good friend / my book / like very much</t>
+          <t>He is my good friend.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>他是我的好朋友。</t>
+          <t>她很喜欢学汉语。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>He is my good friend.</t>
+          <t>She really likes studying Chinese.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>我很喜欢这本书。</t>
+          <t>我的书在桌子上。</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>I like this book very much.</t>
+          <t>My book is on the desk.</t>
         </is>
       </c>
     </row>
@@ -2295,32 +2295,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>买东西、回学校、去公司</t>
+          <t>她喜欢买东西。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>buy things / go back to school / go to the company</t>
+          <t>She likes to go shopping.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>她喜欢买东西。</t>
+          <t>我们一起回学校吧。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>She likes to go shopping.</t>
+          <t>Let's go back to school together.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>我们回学校吧。</t>
+          <t>他每天去图书馆看书。</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Let's go back to school.</t>
+          <t>He goes to the library to read every day.</t>
         </is>
       </c>
     </row>
@@ -2357,32 +2357,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>我们学习、孩子高兴、房间很大</t>
+          <t>我知道他是老师。</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>we study / the child is happy / the room is very big</t>
+          <t>I know that he is a teacher.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>我知道他是老师。</t>
+          <t>她学习好让父母很高兴。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>I know he is a teacher.</t>
+          <t>Her being good at studying makes her parents very happy.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>孩子高兴，妈妈也高兴。</t>
+          <t>他说房间很大，我不信。</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>When the child is happy, mom is happy too.</t>
+          <t>He says the room is very big — I don't believe it.</t>
         </is>
       </c>
     </row>
@@ -2419,32 +2419,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>一杯、两个</t>
+          <t>我买了三本书。</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>one cup (of) / two (of)</t>
+          <t>I bought three books.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>我买了三本书。</t>
+          <t>桌子上有两个苹果。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>I bought three books.</t>
+          <t>There are two apples on the table.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>桌子上有两个苹果。</t>
+          <t>请给我一杯水。</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>There are two apples on the table.</t>
+          <t>Please give me a glass of water.</t>
         </is>
       </c>
     </row>
@@ -2481,32 +2481,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>在学校（学习）、对老师（说）、和朋友（说汉语）</t>
+          <t>他在学校学习汉语。</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>study at school / say (something) to the teacher / speak Chinese with friends</t>
+          <t>He studies Chinese at school.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>他在学校看书。</t>
+          <t>我和同学一起吃饭。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>He reads at school.</t>
+          <t>I eat with my classmates.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>我和同学吃饭。</t>
+          <t>她对老师说了谢谢。</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>I eat with my classmates.</t>
+          <t>She said thank you to the teacher.</t>
         </is>
       </c>
     </row>
@@ -2543,32 +2543,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>桌子上、饭店里、椅子下边</t>
+          <t>书在桌子上。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>on the table / in the restaurant / under the chair</t>
+          <t>The book is on the desk.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>书在桌子上。</t>
+          <t>他在房间里看书。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The book is on the table.</t>
+          <t>He is reading in the room.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>他在房间里看书。</t>
+          <t>猫在椅子下边。</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>He is reading in the room.</t>
+          <t>The cat is under the chair.</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>那个饭店怎么样？</t>
+          <t>那件衣服多少钱？</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>How is that restaurant?</t>
+          <t>How much is that piece of clothing?</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>你多吃一点儿。</t>
+          <t>他认真地听老师讲课。</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Eat a little more.</t>
+          <t>He listens attentively to the teacher's lesson.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>她每天学习中文。</t>
+          <t>她在学习中文。</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>She studies Chinese every day.</t>
+          <t>She is studying Chinese.</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>走吧！</t>
+          <t>去吧！</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Let's go!</t>
+          <t>Go ahead!</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>今天真冷啊！</t>
+          <t>今天真冷！</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>这里真漂亮啊！</t>
+          <t>这里真漂亮！</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>爸爸每天开车上班。</t>
+          <t>爸爸开车上班。</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Dad drives to work every day.</t>
+          <t>Dad drives to work.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>I want to ask you a question.</t>
+          <t>I'll ask you a question.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>我买了一些苹果。</t>
+          <t>我吃了早饭，就出门了。</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>I bought some apples.</t>
+          <t>After eating breakfast, I went out.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>天黑了，我们回家吧。</t>
+          <t>晚了，我们回家吧。</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>It's gotten dark — let's go home.</t>
+          <t>It's late — let's go home.</t>
         </is>
       </c>
     </row>
@@ -4339,32 +4339,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>同学们在/正在上课。</t>
+          <t>同学们正在上课。</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>The students are in class (right now).</t>
+          <t>The students are in class right now.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>妈妈在做饭。</t>
+          <t>妈妈在做饭，请别打扰她。</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Mom is cooking.</t>
+          <t>Mom is cooking — please don't disturb her.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>他正在看书。</t>
+          <t>他正在写作业，我等一下再问他。</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>He is reading right now.</t>
+          <t>He is doing homework right now; I'll ask him in a bit.</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>王老师在/正在打电话呢。</t>
+          <t>王老师在打电话呢。</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4510,32 +4510,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>这本书二十四块（钱）。</t>
+          <t>这本书二十四块。</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>This book costs twenty-four yuan.</t>
+          <t>This book costs 24 yuan.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>包子三块（钱）一个。</t>
+          <t>包子三块钱一个。</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Steamed buns are three yuan each.</t>
+          <t>Steamed buns are 3 yuan each.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>那件衣服一百八十五块五毛。</t>
+          <t>那件衣服一百八十五块。</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>That piece of clothing costs 185 yuan and 50 fen.</t>
+          <t>That piece of clothing costs 185 yuan.</t>
         </is>
       </c>
     </row>
@@ -4624,32 +4624,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2022年2月4日</t>
+          <t>她的生日是一九九八年六月二十日，星期六。</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>February 4, 2022</t>
+          <t>Her birthday is Saturday, June 20, 1998.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>九月十五号、五月一日</t>
+          <t>他的生日是五月一号。</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>September 15th; May 1st</t>
+          <t>His birthday is May 1st.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>星期一、星期二、星期三、星期四、星期五、星期六、星期日/星期天</t>
+          <t>我们每个星期三上汉语课。</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday, Saturday, Sunday</t>
+          <t>We have Chinese class every Wednesday.</t>
         </is>
       </c>
     </row>
@@ -4681,32 +4681,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>两点、七点零五、九点二十（分）、十点半</t>
+          <t>现在七点半，我们快走吧。</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2:00; 7:05; 9:20; 10:30</t>
+          <t>It's 7:30 now — let's hurry.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>现在几点了？——三点零八分。</t>
+          <t>我们九点二十开始上课。</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>What time is it now? — 3:08.</t>
+          <t>Our class starts at 9:20.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>我们八点半上课。</t>
+          <t>他每天两点睡觉，太晚了。</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>We start class at 8:30.</t>
+          <t>He goes to sleep at 2 o'clock every day — that's too late.</t>
         </is>
       </c>
     </row>
@@ -4862,32 +4862,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>那本书能给我看看吗？</t>
+          <t>你说一说，为什么选这个答案。</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Could you let me have a look at that book?</t>
+          <t>Tell us a bit about why you chose this answer.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>请大家说一说自己的爱好。</t>
+          <t>他想了想，最后同意了。</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Everyone, please talk a little about your own hobbies.</t>
+          <t>He thought it over and finally agreed.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>我尝了尝，觉得很好吃。</t>
+          <t>你去休息休息吧，别太累了。</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>I had a taste and thought it was delicious.</t>
+          <t>Go rest for a bit; don't get too tired.</t>
         </is>
       </c>
     </row>
@@ -4996,22 +4996,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>晚上一起去游游泳，运动一下吧。</t>
+          <t>她昨天游了一个小时泳。</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Let's go for a swim together tonight and get some exercise.</t>
+          <t>She swam for an hour yesterday.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>星期六的晚上，我喜欢和朋友们一起唱唱歌，跳跳舞。</t>
+          <t>我喜欢跳舞，每天早上跑半个小时步。</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>On Saturday evenings I like to sing and dance with my friends.</t>
+          <t>I love dancing and run for half an hour every morning.</t>
         </is>
       </c>
     </row>
@@ -5172,32 +5172,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>他为什么学得那么好？</t>
+          <t>你这样做是对的。</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Why does he study so well?</t>
+          <t>Doing it this way is correct.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>那样的事情经常有。</t>
+          <t>那么好的机会，你怎么那样错过了？</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>That kind of thing happens all the time.</t>
+          <t>Such a good opportunity — how did you miss it like that?</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>这么多人，我们明天再来吧。</t>
+          <t>这么好的天气，我每天都想出去走走。</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>There are so many people — let's come back tomorrow.</t>
+          <t>With such nice weather, I want to go for a walk every day.</t>
         </is>
       </c>
     </row>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>那个小孩儿的手圆圆的，很好看。</t>
+          <t>那个小孩儿的手小小的，很好看。</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>That child's hands are so round and pretty.</t>
+          <t>That child's hands are so small and pretty.</t>
         </is>
       </c>
     </row>
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>两万三千、五万零八百、二十多年、五十多人</t>
+          <t>这个市场有好多好吃的东西。</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>23,000; 50,800; more than twenty years; more than fifty people</t>
+          <t>This market has so many delicious things.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>这里有很多好吃的。</t>
+          <t>他在中国住了三十多年了。</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>There's a lot of good food here.</t>
+          <t>He has lived in China for more than 30 years.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>他在中国住了三十多年了。</t>
+          <t>这套房子要两万五千块钱。</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>He has lived in China for over thirty years.</t>
+          <t>This apartment costs 25,000 yuan.</t>
         </is>
       </c>
     </row>
@@ -5353,32 +5353,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>一条裤子、一位老师、一间教室、一名学生</t>
+          <t>我们学校有两位外国老师。</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>a pair of trousers; a teacher; a classroom; a student</t>
+          <t>Our school has two foreign teachers.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>这条路很长，也很漂亮。</t>
+          <t>他买了一条新裤子，还租了一间小房间。</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>This road is very long and also very beautiful.</t>
+          <t>He bought a new pair of pants and also rented a small room.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>我们学校有三十多间教室。</t>
+          <t>这次比赛有五十名学生参加。</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Our school has more than thirty classrooms.</t>
+          <t>Fifty students participated in this competition.</t>
         </is>
       </c>
     </row>
@@ -5415,32 +5415,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>一包衣服、一包书</t>
+          <t>请给我一包茶叶。</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>a bag of clothes; a bundle of books</t>
+          <t>Please give me a pack of tea leaves.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>她带了两包东西来。</t>
+          <t>他买了两包咖啡。</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>She brought two bags of things.</t>
+          <t>He bought two packs of coffee.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>请给我一包米。</t>
+          <t>桌子上有一包糖，你吃吧。</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Please give me a bag of rice.</t>
+          <t>There's a bag of candy on the table — help yourself.</t>
         </is>
       </c>
     </row>
@@ -5477,32 +5477,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>去一次、看一次</t>
+          <t>我去过北京两次。</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>go once; see/watch it once</t>
+          <t>I have been to Beijing twice.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>我去过北京两次。</t>
+          <t>这个电影我看了三次，还是很好看。</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>I've been to Beijing twice.</t>
+          <t>I've watched this film three times and it's still great.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>这部电影我看了三次。</t>
+          <t>请再说一次，我没听清楚。</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>I've watched this movie three times.</t>
+          <t>Please say it one more time — I didn't hear clearly.</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>我们一起去吃饭，好吗？</t>
+          <t>你可以和我一起学习吗？</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Let's go eat together, okay?</t>
+          <t>Can you study together with me?</t>
         </is>
       </c>
     </row>
@@ -5663,32 +5663,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>他还没有起床呢。</t>
+          <t>他还没起床，有时候都睡到十点。</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>He still hasn't gotten up yet.</t>
+          <t>He still hasn't gotten up; sometimes he sleeps until ten.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>张老师已经下班了。</t>
+          <t>我正在吃饭，饭已经好了，你来得正好。</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Teacher Zhang has already finished work.</t>
+          <t>I'm just eating; the meal is already ready — you've come at just the right time.</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>我有时（候）去超市买东西。</t>
+          <t>快要下课了，快点写完作业。</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>I sometimes go to the supermarket to shop.</t>
+          <t>Class is about to end; hurry and finish the homework.</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>我先休息一会儿再工作。</t>
+          <t>我休息一会儿再工作。</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>I'll rest for a bit first, then get to work.</t>
+          <t>I'll rest for a bit, then get to work.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>就买这件白色的吧。</t>
+          <t>你还是早点儿睡觉吧。</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Just buy this white one.</t>
+          <t>You'd better go to sleep early.</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>从学校到家，你要走多久？</t>
+          <t>从学校到家，要走多长时间？</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>请给我一杯水。</t>
+          <t>请给我介绍一下这个地方。</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Please get me a glass of water.</t>
+          <t>Please introduce this place to me.</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6365,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>因为下雨，他来晚了。</t>
+          <t>因为工作，他很少回家。</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Because of the rain, he arrived late.</t>
+          <t>Because of work, he rarely goes home.</t>
         </is>
       </c>
     </row>
@@ -6469,32 +6469,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>这家饭馆的菜很好吃，但/但是有点儿贵。</t>
+          <t>那你就自己去吧，我不去了。</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>The food at this restaurant is delicious, but it's a bit expensive.</t>
+          <t>In that case, you go yourself; I'm not going.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>你不舒服，那就别去了。</t>
+          <t>他很累，但还是坚持工作。</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>You're not feeling well, so in that case don't go.</t>
+          <t>He was very tired, but still kept working.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>手机虽然不大，但/但是能帮我们做很多事。</t>
+          <t>因为今天下雨，所以我没出去。</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Although a phone is small, it can help us do many things.</t>
+          <t>Because it's raining today, I didn't go out.</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>你吃过北京烤鸭吗？</t>
+          <t>你吃过中国菜吗？</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Have you ever eaten Peking duck?</t>
+          <t>Have you ever eaten Chinese food?</t>
         </is>
       </c>
     </row>
@@ -6675,12 +6675,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>他们唱着歌，跳着舞，非常高兴。</t>
+          <t>他们唱着歌，笑着，非常高兴。</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>They were singing and dancing, very happy.</t>
+          <t>They were singing and laughing, very happy.</t>
         </is>
       </c>
     </row>
@@ -6717,32 +6717,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>她怎么不在家呢？</t>
+          <t>你到底去不去呢？</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>How come she's not home?</t>
+          <t>Are you actually going or not?</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>明天你想去哪儿呢？</t>
+          <t>外面很冷，你多穿点儿衣服吧。</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Where do you want to go tomorrow?</t>
+          <t>It's cold outside — put on a few more layers.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>这是你的手机吧？</t>
+          <t>这件事我早就知道的，别担心啊！</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>This is your phone, right?</t>
+          <t>I've known about this for a long time — don't worry!</t>
         </is>
       </c>
     </row>
@@ -6779,32 +6779,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>听懂、回去、跑得很快、等一下</t>
+          <t>老师说的话，你听懂了吗？</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>understand (by listening); go back; run very fast; wait a moment</t>
+          <t>Did you understand what the teacher said?</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>老师说的，你听懂了吗？</t>
+          <t>他跑得很快，我跟不上。</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Did you understand what the teacher said?</t>
+          <t>He runs very fast — I can't keep up.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>他跑得很快，我跟不上。</t>
+          <t>这篇文章我看完了，写得很好。</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>He runs very fast — I can't keep up.</t>
+          <t>I finished reading this article — it's written very well.</t>
         </is>
       </c>
     </row>
@@ -6841,32 +6841,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>老师的、白色的、便宜的、妈妈做的</t>
+          <t>这件是我的，那件是她的。</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>the teacher's (one); the white one; the cheap one; the one Mom made</t>
+          <t>This one is mine; that one is hers.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>这件是我的，那件是她的。</t>
+          <t>妈妈做的菜最好吃。</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>This one is mine; that one is hers.</t>
+          <t>The food Mom makes is the most delicious.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>我想要便宜的，不要贵的。</t>
+          <t>便宜的不一定不好。</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>I want the cheap one, not the expensive one.</t>
+          <t>Cheap things aren't necessarily bad.</t>
         </is>
       </c>
     </row>
@@ -6903,32 +6903,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>来上课、去上海旅游、坐地铁去学校</t>
+          <t>我每天走路去上班。</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>come to class; go to Shanghai to travel; take the subway to school</t>
+          <t>I walk to work every day.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>我每天走路去上班。</t>
+          <t>他坐地铁去学校。</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>I walk to work every day.</t>
+          <t>He takes the subway to school.</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>她去学校看书了。</t>
+          <t>她去图书馆借了一本书。</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>She went to school to read.</t>
+          <t>She went to the library and borrowed a book.</t>
         </is>
       </c>
     </row>
@@ -6965,32 +6965,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>请他来、叫朋友帮忙、让妈妈洗衣服</t>
+          <t>妈妈让我去买东西。</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>invite him to come; ask a friend to help; have Mom do the laundry</t>
+          <t>Mom asked me to go shopping.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>妈妈让我去买东西。</t>
+          <t>老师叫我们写一篇作文。</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Mom asked me to go buy things.</t>
+          <t>The teacher asked us to write a composition.</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>老师叫我们写字。</t>
+          <t>他请朋友来家里吃饭。</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>The teacher asked us to write characters.</t>
+          <t>He invited his friend to come eat at his place.</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7022,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>新电脑、老师的书、火车票、一个男孩、两条、这间</t>
+          <t>那个红色的包是我的。</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>a new computer; the teacher's book; a train ticket; a boy; two (of them); this one (room)</t>
+          <t>That red bag is mine.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>那个红色的包是我的。</t>
+          <t>两杯咖啡，多少钱？</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>That red bag is mine.</t>
+          <t>How much for two cups of coffee?</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>两杯咖啡，多少钱？</t>
+          <t>这张火车票是她买的。</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Two cups of coffee — how much is that?</t>
+          <t>This train ticket was bought by her.</t>
         </is>
       </c>
     </row>
@@ -7079,32 +7079,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>写汉字、听懂、回去、经常上网、可以进去</t>
+          <t>他每天晚上看书。</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>write Chinese characters; understand (by listening); go back; often go online; be allowed to go in</t>
+          <t>He reads every evening.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>他每天晚上经常看书。</t>
+          <t>你可以进去，门开着呢。</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>He often reads every evening.</t>
+          <t>You can go in — the door is open.</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>你可以进去，门开着呢。</t>
+          <t>我经常上网买东西。</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>You can go in — the door is open.</t>
+          <t>I often shop online.</t>
         </is>
       </c>
     </row>
@@ -7136,32 +7136,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>很累、非常忙、慢一点儿</t>
+          <t>今天的天气非常好。</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>very tired; extremely busy; a bit slower</t>
+          <t>The weather today is excellent.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>今天的天气非常好。</t>
+          <t>请说慢一点儿，我听不懂。</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>The weather today is extremely nice.</t>
+          <t>Please speak a bit more slowly — I can't understand.</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>请说慢一点儿，我听不懂。</t>
+          <t>走了这么多路，我很累。</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Please speak a bit slower — I can't understand.</t>
+          <t>After walking so far, I'm very tired.</t>
         </is>
       </c>
     </row>
@@ -7354,32 +7354,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>都这么晚了，你怎么还不睡觉？</t>
+          <t>都十二点了，你怎么还不睡？</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>It's already so late — why are you still not asleep?</t>
+          <t>It's already midnight — why aren't you asleep?</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>都十一点了，快去睡觉吧！</t>
+          <t>都吃了三碗饭了，你还要吃？</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>It's already eleven o'clock — go to sleep quickly!</t>
+          <t>You've already eaten three bowls — you want more?</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>都八点了，快走吧！</t>
+          <t>都说了好几次了，你怎么还是不记得？</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>It's already eight o'clock — let's go!</t>
+          <t>I've said it so many times already — how do you still not remember?</t>
         </is>
       </c>
     </row>
@@ -7421,17 +7421,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>那本书我看过了。</t>
+          <t>桌子已经擦干净了。</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>That book — I've already read it.</t>
+          <t>The table has already been wiped clean.</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>这道菜做好了。</t>
+          <t>这个菜做好了。</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>她高个子、大眼睛，很漂亮。</t>
+          <t>她高个子、大眼睛。</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>She is tall with big eyes — very pretty.</t>
+          <t>She is tall with big eyes.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Teacher Wang is from Shanghai and is in his/her forties.</t>
+          <t>Teacher Wang is from Shanghai and is in their forties.</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7587,32 +7587,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>这个字你写错了。</t>
+          <t>这个字我写错了，让我重新写。</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>You wrote this character wrong.</t>
+          <t>I wrote this character wrong; let me rewrite it.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>你听懂老师说的了吗？</t>
+          <t>作业做完了，他也学会了这个词的用法。</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Did you understand what the teacher said?</t>
+          <t>The homework is done, and he has also learned how to use this word.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>衣服已经洗好了。</t>
+          <t>饭做好了，你快把书收好，来吃饭吧。</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The clothes have already been washed.</t>
+          <t>The meal is ready — quickly put your book away and come eat.</t>
         </is>
       </c>
     </row>
@@ -7669,12 +7669,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>他走进来，看了看，就走出去了。</t>
+          <t>她笑着走来了。</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>He walked in, looked around, and then walked out.</t>
+          <t>She came walking over with a smile.</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>飞机飞上天了。</t>
+          <t>他走出教室，又跑回家去拿书。</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>The plane flew up into the sky.</t>
+          <t>He walked out of the classroom and ran back home to get his book.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>弟弟跑下楼了。</t>
+          <t>请把车开进车库，然后把行李搬下来。</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>My younger brother ran downstairs.</t>
+          <t>Please drive the car into the garage, then bring the luggage down.</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>她走进房间了。</t>
+          <t>他从我身边走过，没有停下来，后来慢慢爬上了山顶。</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>She walked into the room.</t>
+          <t>He walked past me without stopping, and later slowly climbed up to the top of the mountain.</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>这本书故事很有意思。</t>
+          <t>这本书名字很好听。</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>This book — its story is very interesting.</t>
+          <t>This book's title is very nice.</t>
         </is>
       </c>
     </row>
@@ -8207,32 +8207,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>那件衣服是新的。</t>
+          <t>这件毛衣是红色的。</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>That piece of clothing is new.</t>
+          <t>This sweater is red.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>这个手机是坏的，不能用。</t>
+          <t>这件衣服是新的，很好看。</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>This phone is broken — it can't be used.</t>
+          <t>This piece of clothing is new and looks great.</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>这个苹果是甜的。</t>
+          <t>那个地方的风景是很美的。</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>This apple is sweet.</t>
+          <t>The scenery in that place is very beautiful.</t>
         </is>
       </c>
     </row>
@@ -8279,22 +8279,22 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>这些水果有一百块钱吗？</t>
+          <t>这袋米有五公斤。</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Do these fruits cost as much as a hundred yuan?</t>
+          <t>This bag of rice weighs a full five kilograms.</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>这条路有一百米吗？</t>
+          <t>这条路有没有一百公里长？</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Is this road as long as a hundred meters?</t>
+          <t>Is this road a hundred kilometers long or not?</t>
         </is>
       </c>
     </row>
@@ -8351,12 +8351,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>床上躺着一只猫。</t>
+          <t>桌上趴着一只猫。</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>There is a cat lying on the bed.</t>
+          <t>A cat is lying crouched on the table.</t>
         </is>
       </c>
     </row>
@@ -8527,22 +8527,22 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>今天没有昨天（那么）冷。</t>
+          <t>今天没有昨天那么冷。</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Today is not as cold as yesterday.</t>
+          <t>Today isn't as cold as yesterday.</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>我的汉语没有你（这么）好。</t>
+          <t>我的汉语没有你这么好。</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>My Chinese is not as good as yours.</t>
+          <t>My Chinese isn't as good as yours.</t>
         </is>
       </c>
     </row>
@@ -8661,12 +8661,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>他们是坐飞机去上海的。</t>
+          <t>这本书是他写的。</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>They went to Shanghai by plane.</t>
+          <t>This book was written by him.</t>
         </is>
       </c>
     </row>
@@ -8785,12 +8785,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>我写给她一封信。</t>
+          <t>妈妈做给我们一顿好饭，表示庆祝。</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>I wrote her a letter.</t>
+          <t>Mom made us a good meal to celebrate.</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>你（是）喝茶，还是喝咖啡？</t>
+          <t>你是喝茶，还是喝咖啡？</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8837,22 +8837,22 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>你（是）喜欢白色的，还是黑色的？</t>
+          <t>明天是你去，还是他去？</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Do you like the white one or the black one?</t>
+          <t>Is it you or him going tomorrow?</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>你（是）坐飞机去，还是坐火车去？</t>
+          <t>你是去还是留，自己决定吧。</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Are you going by plane or by train?</t>
+          <t>Whether you go or stay — decide for yourself.</t>
         </is>
       </c>
     </row>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>学汉语虽然难，但是很有意思。</t>
+          <t>那家饭馆虽然贵，但是很好吃。</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Although learning Chinese is hard, it's very interesting.</t>
+          <t>Although that restaurant is expensive, the food is very delicious.</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9090,12 +9090,12 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>灯开着，电费很贵。</t>
+          <t>她戴着耳机，没有听到我说话。</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>The light is on — electricity is expensive.</t>
+          <t>She had her headphones on and didn't hear me speak.</t>
         </is>
       </c>
     </row>
@@ -9432,12 +9432,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>我们走了一个小时多才到那里。</t>
+          <t>我们走了一个小时多，到了那里。</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>We walked for over an hour before we got there.</t>
+          <t>We walked for over an hour and arrived there.</t>
         </is>
       </c>
     </row>
@@ -9650,32 +9650,32 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>从这儿过去，大概需要多长时间？</t>
+          <t>你应该多喝水，注意身体。</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>How long does it roughly take to get there from here?</t>
+          <t>You should drink more water and take care of your health.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>医生说我感冒了，需要吃药。</t>
+          <t>他不愿意去，我们也不能强迫他。</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>The doctor said I have a cold and need to take medicine.</t>
+          <t>He's unwilling to go; we can't force him.</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>已经十一点了，你该睡觉了。</t>
+          <t>你需要多休息，明天还得上班呢。</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>It's already eleven o'clock — you should go to sleep.</t>
+          <t>You need to rest more — you still have to go to work tomorrow.</t>
         </is>
       </c>
     </row>
@@ -9722,22 +9722,22 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>我们已经很长时间没见过面了。</t>
+          <t>我们很久没见过面了，她上个月刚结了婚。</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>We haven't seen each other for a very long time.</t>
+          <t>We haven't seen each other for a long time — she just got married last month.</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>结了婚以后，你还打算工作吗？</t>
+          <t>她洗了半个小时澡，才出来。</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>After you get married, do you still plan to work?</t>
+          <t>She bathed for half an hour before coming out.</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>他已经离不开这个地方了。</t>
+          <t>他们离开家乡后，才完成了任务，最终分开了。</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>He can no longer leave this place.</t>
+          <t>After leaving their hometown, they completed the task and eventually went their separate ways.</t>
         </is>
       </c>
     </row>
@@ -9898,12 +9898,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>这个活动谁都可以参加。</t>
+          <t>这个比赛谁都可以参加。</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Anyone can join this activity.</t>
+          <t>Anyone can participate in this competition.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10228,12 +10228,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>他喝了两碗汤，好多了。</t>
+          <t>他喝了两碗水，好多了。</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>He drank two bowls of soup and felt much better.</t>
+          <t>He drank two bowls of water and felt much better.</t>
         </is>
       </c>
     </row>
@@ -10270,32 +10270,32 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>他喝了一口茶，然后开始工作。</t>
+          <t>他喝了一口茶，说了两声谢谢。</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>He took a sip of tea, then started working.</t>
+          <t>He took a sip of tea and said thank you twice.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>我已经说过好几回了，但他还是不记得。</t>
+          <t>这篇课文我读了好几遍。</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>I've already said it several times, but he still doesn't remember.</t>
+          <t>I've read this text several times.</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>对不起，我没听懂，请说一遍。</t>
+          <t>他来过这里两回了，很熟悉这里。</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Sorry, I didn't understand — please say it once more from the beginning.</t>
+          <t>He's been here twice; he's very familiar with the place.</t>
         </is>
       </c>
     </row>
@@ -10394,32 +10394,32 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>这本书比较简单，我读得很快。</t>
+          <t>这本书比较难，那本更难。</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>This book is relatively simple, so I read it quickly.</t>
+          <t>This book is fairly difficult; that one is even harder.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>外面太热了，屋子里还凉快一些。</t>
+          <t>今天的考试特别难，很多人没考好。</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>It's too hot outside; it's a bit cooler inside.</t>
+          <t>Today's exam was especially difficult — many people didn't do well.</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>搬家以后，我们的生活更方便了。</t>
+          <t>有些题越想越复杂。</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>After moving, our life has become even more convenient.</t>
+          <t>Some questions seem more complex the more you think about them.</t>
         </is>
       </c>
     </row>
@@ -10456,32 +10456,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>我就要两斤苹果，不要别的。</t>
+          <t>我们一块儿去吧，路上有伴儿。</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>I just want two jin of apples — nothing else.</t>
+          <t>Let's go together; it's good to have company on the way.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>办公室里就张老师。</t>
+          <t>他到处找钥匙，一共找了半个小时。</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>There's only Teacher Zhang in the office.</t>
+          <t>He searched everywhere for his keys and spent half an hour in total.</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>你跟我一块儿去图书馆，好吗？</t>
+          <t>他只喝了一杯，就走了，只是没跟大家说一声。</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Come to the library with me, okay?</t>
+          <t>He only had one drink and then just left — it's just that he didn't say a word to anyone.</t>
         </is>
       </c>
     </row>
@@ -10518,32 +10518,32 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>他才到家，还没有吃饭呢。</t>
+          <t>他刚刚打来电话，说马上到。</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>He just got home and hasn't eaten yet.</t>
+          <t>He just called, saying he'll be here right away.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>我才搬来北京，还不太习惯这里的生活</t>
+          <t>我一直等到八点，他才来。</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>I just moved to Beijing and am not quite used to life here yet.</t>
+          <t>I waited until eight o'clock before he came.</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>请等一下，我马上来。</t>
+          <t>你先坐，我去倒杯水来。</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Please wait a moment — I'll be right there.</t>
+          <t>Have a seat first; I'll go get some water.</t>
         </is>
       </c>
     </row>
@@ -10590,22 +10590,22 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>上学的时候，我总是让爸爸开车送我。</t>
+          <t>她总是这么认真，大家都很佩服她。</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>When I was in school, I always had my dad drive me.</t>
+          <t>She's always so conscientious; everyone admires her.</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>那个电影太有意思了，我昨天又看了一遍。</t>
+          <t>他又迟到了，这种事常常发生。</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>That movie was so interesting — I watched it again yesterday.</t>
+          <t>He was late again; this kind of thing happens often.</t>
         </is>
       </c>
     </row>
@@ -10704,32 +10704,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>他大概已经回家了。</t>
+          <t>她好像有点儿不舒服，几乎不说话。</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>He has probably already gone home.</t>
+          <t>She seems a bit unwell; she barely says a word.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>你们学校大概有多少留学生？</t>
+          <t>你必须按时到，一定不能迟到。</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Roughly how many international students does your school have?</t>
+          <t>You must arrive on time; you absolutely cannot be late.</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>我必须做完作业才下班。</t>
+          <t>大概还需要差不多一个小时。</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>I must finish the homework before I get off work.</t>
+          <t>It will probably take about another hour.</t>
         </is>
       </c>
     </row>
@@ -10766,32 +10766,32 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>我当然愿意帮助你。</t>
+          <t>当然可以，你来就行了。</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Of course I'm willing to help you.</t>
+          <t>Of course you can — just come.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>当然没问题，欢迎你参加。</t>
+          <t>其实他早就知道了。</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Of course, no problem — you're welcome to join.</t>
+          <t>Actually he knew all along.</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>这个问题其实不难。</t>
+          <t>等了很久，车终于来了，他才上车。</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>This question is actually not difficult.</t>
+          <t>After waiting a long time, the bus finally came and he got on.</t>
         </is>
       </c>
     </row>
@@ -10838,12 +10838,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>不用担心，我们帮你一起准备。</t>
+          <t>不必担心，他很快就会回来的。</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Don't worry — we'll help you prepare.</t>
+          <t>There's no need to worry — he'll be back soon.</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10900,22 +10900,22 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>大家为这次比赛做了很多准备。</t>
+          <t>他向老师提了一个问题。</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Everyone made a lot of preparations for this competition.</t>
+          <t>He directed a question at the teacher.</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>如果你不能去上课，应该向老师请假。</t>
+          <t>关于这件事，我还有一些问题想问你。</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>If you can't attend class, you should ask the teacher for leave.</t>
+          <t>Regarding this matter, I still have some questions for you.</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Mom often stays up very late because of work.</t>
+          <t>Mom often stays up late for the sake of work.</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11200,32 +11200,32 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>我喝茶或/或者咖啡都可以。</t>
+          <t>你可以坐公共汽车或坐地铁去。</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Either tea or coffee is fine with me.</t>
+          <t>You can get there by bus or by subway.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>我们可以打车或/或者坐地铁去。</t>
+          <t>这个周末或者下个周末，我们可以去爬山。</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>We can take a taxi or the subway to get there.</t>
+          <t>This weekend or next weekend, we could go hiking.</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>你可以打电话或者发短信给我。</t>
+          <t>喝茶或者喝咖啡，你选吧。</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>You can call me or send me a text.</t>
+          <t>Tea or coffee — you choose.</t>
         </is>
       </c>
     </row>
@@ -11262,32 +11262,32 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>只有每天练习，才会说好中文。</t>
+          <t>只要你努力，就一定能成功。</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Only by practicing every day will you be able to speak Chinese well.</t>
+          <t>As long as you work hard, you will definitely succeed.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>只要你想学，就一定能学好。</t>
+          <t>他不但成绩好，而且待人热情。</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>As long as you want to learn, you will definitely be able to learn it well.</t>
+          <t>He not only has good grades but is also warm to people.</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>我不但学习了中文，而且认识了很多新朋友。</t>
+          <t>我想去，可是没有时间。</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Not only did I study Chinese, but I also made many new friends.</t>
+          <t>I want to go, but I don't have time.</t>
         </is>
       </c>
     </row>
@@ -11386,22 +11386,22 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>城市上海、我的老师王老师、我们同学</t>
+          <t>我的老师王老师教我们汉语。</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>The city Shanghai / My teacher, Teacher Wang / We classmates</t>
+          <t>My teacher, Teacher Wang, teaches us Chinese.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>我的老师王老师教我们汉语。</t>
+          <t>我去了首都北京旅游。</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>My teacher, Teacher Wang, teaches us Chinese.</t>
+          <t>I went to travel in Beijing, the capital.</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -11448,32 +11448,32 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>漂亮极了、累坏了、看不懂、写得完</t>
+          <t>这本书我看不懂，太难了。</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Extremely beautiful; exhausted; can't understand (from reading); able to finish writing</t>
+          <t>I can't understand this book — it's too difficult.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>这本书我看不懂，太难了。</t>
+          <t>今天的作业不多，我写得完。</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>I can't understand this book; it's too difficult.</t>
+          <t>There isn't much homework today — I can finish it.</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>今天的作业不多，我写得完。</t>
+          <t>他跑得太快了，我追不上。</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>There isn't much homework today; I can finish writing it.</t>
+          <t>He runs too fast — I can't catch up.</t>
         </is>
       </c>
     </row>
@@ -11510,12 +11510,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>工作要一步一步地做。</t>
+          <t>他一件一件地做完了工作。</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Work should be done step by step.</t>
+          <t>He completed the work one task at a time.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>他一步一步地走上山。</t>
+          <t>她一个一个地回答问题。</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>He walked up the mountain step by step.</t>
+          <t>She answered the questions one by one.</t>
         </is>
       </c>
     </row>
@@ -11644,12 +11644,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>时间不一会儿就过去了。</t>
+          <t>不一会儿，他就回来了。</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Time passed in no time at all.</t>
+          <t>In no time, he was back.</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>这道题看上去很难，其实很简单。</t>
+          <t>这个问题看上去很难，其实很简单。</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12120,32 +12120,32 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>除了看新闻（以外），人们还/也可以在网上看电影、买东西。</t>
+          <t>除了汉语以外，她还会说英语。</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Besides reading the news, people can also watch movies and shop online.</t>
+          <t>Besides Chinese, she can also speak English.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>除了北京（以外），别的城市我都没去过。</t>
+          <t>除了他以外，大家都同意了。</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Except for Beijing, I haven't been to any other cities.</t>
+          <t>Except for him, everyone agreed.</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>除了汉语以外，她还会说英语。</t>
+          <t>除了北京，别的城市我都没去过。</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>In addition to Chinese, she can also speak English.</t>
+          <t>I haven't been to any city other than Beijing.</t>
         </is>
       </c>
     </row>
@@ -12452,12 +12452,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>睡觉前别忘记吃药。</t>
+          <t>吃饭后，他去散步了。</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Don't forget to take your medicine before bed.</t>
+          <t>After eating, he went for a walk.</t>
         </is>
       </c>
     </row>
@@ -12722,12 +12722,12 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>他工作很努力让大家都很高兴。</t>
+          <t>他工作很努力，这让大家都很高兴。</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>That he works so hard makes everyone happy.</t>
+          <t>He works very hard — this makes everyone very happy.</t>
         </is>
       </c>
     </row>
@@ -12769,12 +12769,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>前面那个蓝衣服短头发的高个子男人是我的中文老师。</t>
+          <t>前面那个穿蓝衣服、留短头发的高个子男人是我的中文老师。</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>That tall man with short hair in the blue clothes up ahead is my Chinese teacher.</t>
+          <t>That tall man in front wearing a blue shirt with short hair is my Chinese teacher.</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>这道题太难，他做不对。</t>
+          <t>这个问题太难，他做不对。</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>This question is too hard; he can't get it right.</t>
+          <t>This question is too hard — he can't get it right.</t>
         </is>
       </c>
     </row>
@@ -13213,12 +13213,12 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>今天没带伞，又碰到下雨，气坏了。</t>
+          <t>她丢了钱包，难过极了。</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>I didn't bring an umbrella today and it started raining — I was absolutely furious.</t>
+          <t>She lost her wallet and was extremely sad.</t>
         </is>
       </c>
     </row>
@@ -13327,22 +13327,22 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>中国人是怎样过新年的？</t>
+          <t>你怎样去学校，坐地铁还是骑车？</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>How do Chinese people celebrate the New Year?</t>
+          <t>How do you get to school — by subway or by bike?</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>你的新工作怎样？</t>
+          <t>你打算怎样解决这个问题？</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>How is your new job?</t>
+          <t>How do you plan to solve this problem?</t>
         </is>
       </c>
     </row>
@@ -13441,12 +13441,12 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>你把箱子放在这儿吧。</t>
+          <t>请把椅子搬到教室里去。</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Put the suitcase here.</t>
+          <t>Please move the chairs into the classroom.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>他把车停在学校门口了。</t>
+          <t>我把书包放在椅子上了。</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>He parked the car at the school entrance.</t>
+          <t>I put my school bag on the chair.</t>
         </is>
       </c>
     </row>
@@ -13585,12 +13585,12 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>妈妈把衣服洗得干干净净。</t>
+          <t>妈妈把衣服洗干净了。</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Mom washed the clothes spotlessly clean.</t>
+          <t>Mom washed the clothes clean.</t>
         </is>
       </c>
     </row>
@@ -13647,12 +13647,12 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>他的手机被弟弟摔坏了。</t>
+          <t>他的书被弟弟拿走了。</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>His phone was dropped and broken by his younger brother.</t>
+          <t>His book was taken away by his younger brother.</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>那扇门被打开了。</t>
+          <t>那个门被打开了。</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>她比我晚睡一个小时。</t>
+          <t>你今天比昨天少喝了一杯咖啡。</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>She went to sleep one hour later than me.</t>
+          <t>You drank one fewer cup of coffee today than yesterday.</t>
         </is>
       </c>
     </row>
@@ -14128,7 +14128,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>A taxi came driving from up ahead.</t>
+          <t>A taxi drove up from ahead.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14143,12 +14143,12 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>校门外走进来几个学生。</t>
+          <t>校门外走进来了几个学生。</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>A few students walked in through the school gate.</t>
+          <t>A few students walked in from outside the school gate.</t>
         </is>
       </c>
     </row>
@@ -14205,12 +14205,12 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>桌上拿走了两本书。</t>
+          <t>停车场里开走了三辆车。</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>Two books were taken from the table.</t>
+          <t>Three cars drove away from the parking lot.</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>The pivotal verb sentence (重动句) repeats the verb after the object so that a duration or manner complement can be attached. This construction is used when the verb takes an object but also needs a complement, which cannot directly follow the object.</t>
+          <t>A verb-reduplication sentence (重动句) repeats the main verb after its object to add a complement or other element. Pattern: Subject + Verb + Object + Verb + Complement.</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -14681,12 +14681,12 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>不但我学习中文，而且我的弟弟也学习中文。</t>
+          <t>不但我学中文，我弟弟也学中文。</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Not only am I studying Chinese, but my younger brother is too.</t>
+          <t>Not only do I study Chinese, my younger brother does too.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15217,6 +15217,11 @@
           <t>数的表达法</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>概数表达法3</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>概数表达法2：相邻数词连用表示概数</t>
@@ -15363,22 +15368,22 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>节日里，各地举行了很多庆祝活动。</t>
+          <t>此次会议，各位嘉宾请按时到场。</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>During the holiday, various places held many celebrations.</t>
+          <t>For this meeting, all guests are kindly asked to arrive on time.</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>各位同学，请大家安静一下。</t>
+          <t>市场上有各种各样的商品，任何人都可以来购买。</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>Everyone, please quiet down for a moment.</t>
+          <t>The market has all kinds of goods; anyone can come to buy.</t>
         </is>
       </c>
     </row>
@@ -15425,22 +15430,22 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>我买了一打鸡蛋，准备做蛋糕。</t>
+          <t>他买了一袋大米，还在院子里种了一棵树。</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>I bought a dozen eggs to make a cake.</t>
+          <t>He bought a bag of rice and planted a tree in the yard.</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>我这儿有一袋方便面，你想吃吗？</t>
+          <t>书房里放着一台电脑，墙上挂着一幅画。</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>I have a bag of instant noodles here — do you want some?</t>
+          <t>There is a computer in the study, and a painting hangs on the wall.</t>
         </is>
       </c>
     </row>
@@ -15487,22 +15492,22 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>小明见到了自己喜欢的作家，满脸高兴。</t>
+          <t>他手上粘了一手面粉，桌上还放着一盒饼干。</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Xiao Ming met the author he admired and was beaming with happiness.</t>
+          <t>His hand was covered in flour, and a box of cookies sat on the table.</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>他回家时满脸是汗，看起来很累。</t>
+          <t>孩子们把积木撒了一屋子，桌子上也摆了一桌子零食。</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>He came home with a face full of sweat and looked very tired.</t>
+          <t>The children scattered building blocks all over the room, and the table was covered with snacks.</t>
         </is>
       </c>
     </row>
@@ -15549,22 +15554,22 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>同学们都想在中国观看一场京剧演出。</t>
+          <t>周末咱们去饭馆好好吃一顿，怎么样？</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>All the students want to watch a Peking opera performance in China.</t>
+          <t>How about we go to a restaurant and have a proper meal this weekend?</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>周末咱们去饭馆好好吃一顿，怎么样？</t>
+          <t>我特地跑了一趟邮局，把包裹寄出去了。</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>How about we go to a restaurant and have a proper meal this weekend?</t>
+          <t>I made a special trip to the post office to send off the parcel.</t>
         </is>
       </c>
     </row>
@@ -15601,32 +15606,32 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>她十分激动地对我们表示感谢。</t>
+          <t>他十分认真，学习更加努力了。</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>She expressed her thanks to us in a very excited manner.</t>
+          <t>He is extremely conscientious and studies even harder now.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>那位导游对游客十分热情。</t>
+          <t>这道题稍微有点难，尤其是最后一步。</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>That tour guide was extremely warm and enthusiastic toward the tourists.</t>
+          <t>This problem is slightly difficult, especially the last step.</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>随着互联网的发展，网上购物变得更加方便了。</t>
+          <t>天气稍冷，多么美的秋天啊！</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>With the development of the internet, online shopping has become even more convenient.</t>
+          <t>The weather is slightly cool — what a beautiful autumn!</t>
         </is>
       </c>
     </row>
@@ -15663,32 +15668,32 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>上一年大学，学费和生活费共需多少钱？</t>
+          <t>全班同学共二十八人都参加了活动。</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>How much money is needed in total for tuition and living expenses for one year of university?</t>
+          <t>All 28 students in the class participated in the activity.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>中国人习惯一家人共吃一桌菜。</t>
+          <t>光学语法是不够的，还要多说。</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Chinese people are accustomed to the whole family sharing dishes together at the table.</t>
+          <t>Just studying grammar is not enough — you also need to speak more.</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>昨天学习的生词和语法我已经全记住了。</t>
+          <t>这件事仅仅花了他十分钟，至少比我快多了。</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>I have already memorized all the vocabulary and grammar we studied yesterday.</t>
+          <t>This matter took him only ten minutes — at least much faster than me.</t>
         </is>
       </c>
     </row>
@@ -15725,32 +15730,32 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>时间很紧张，但我们必须按时完成任务。</t>
+          <t>他从来不迟到，总是按时到达。</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Time is tight, but we must complete the task on time.</t>
+          <t>He never arrives late; he is always on time.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>医生让我回家按时吃药，多喝热水。</t>
+          <t>快迟到了，赶快走吧。</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>The doctor told me to go home, take my medicine on schedule, and drink plenty of hot water.</t>
+          <t>We are about to be late — let's hurry up and go.</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>我从来没有离开过家乡，父母不放心我出国留学。</t>
+          <t>我本来打算早走，忽然下雨了。</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>I have never left my hometown before, so my parents are worried about me studying abroad.</t>
+          <t>I had originally planned to leave early, but it suddenly started raining.</t>
         </is>
       </c>
     </row>
@@ -15797,22 +15802,22 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>这个问题，您能不能重新考虑一下？</t>
+          <t>其实，一些看起来很小的事情往往会影响人的一生，偶尔反思一下很有必要。</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Could you reconsider this issue?</t>
+          <t>In fact, things that seem trivial often end up affecting a person's entire life — it's worthwhile to reflect from time to time.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>其实，一些看起来很小的事情往往会影响人的一生。</t>
+          <t>他再次犯了同样的错误，老师老是提醒他，可他就是不改。</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>In fact, some things that seem trivial often end up affecting a person's entire life.</t>
+          <t>He made the same mistake again — the teacher keeps reminding him, but he just won't change.</t>
         </is>
       </c>
     </row>
@@ -15869,12 +15874,12 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>我想练习中文，咱们互相学习，互相帮助，怎么样？</t>
+          <t>我们应该相互尊重，互相帮助。</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>I want to practice Chinese — how about we learn from each other and help each other out?</t>
+          <t>We should respect one another and help each other.</t>
         </is>
       </c>
     </row>
@@ -16035,32 +16040,32 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>昨天那场比赛才精彩呢！</t>
+          <t>究竟是谁做的，到底说清楚。</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Now that was a truly exciting match yesterday!</t>
+          <t>Who did it exactly — get it clear once and for all.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>他总是迟到，我才不相信他今天能准时来。</t>
+          <t>千万别说出去，难道你不明白有多严重吗？</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>He's always late — I simply don't believe he'll be on time today.</t>
+          <t>Whatever you do, don't let it out — do you not understand how serious this is?</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>我就知道他肯定会答应的。</t>
+          <t>我差点儿忘了，竟然今天是他生日。</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>I just knew he would definitely agree.</t>
+          <t>I almost forgot — it turns out today is his birthday.</t>
         </is>
       </c>
     </row>
@@ -16097,32 +16102,32 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>自1978年，中国发生了很大的变化。</t>
+          <t>自他来北京工作，就很少回家，当节日到来时才会回去看看。</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Since 1978, China has undergone tremendous change.</t>
+          <t>Since he came to work in Beijing, he has rarely gone home — only when holidays arrive does he go back for a visit.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>我们自北京出发，开车往南走，来到了上海。</t>
+          <t>这次活动由我们班负责组织。</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>We set off from Beijing, drove south, and arrived in Shanghai.</t>
+          <t>This event will be organized by our class.</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>当遇到困难时，先冷静地想一想。</t>
+          <t>随着科技的发展，电脑、手机等新产品已经进入每个家庭。</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>When you encounter difficulties, first calm down and think it through.</t>
+          <t>With the development of technology, new products such as computers and mobile phones have entered every household.</t>
         </is>
       </c>
     </row>
@@ -16159,32 +16164,32 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>离开教室时，请将垃圾带走，并将门窗关好。</t>
+          <t>我的手机让弟弟摔坏了。</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>When leaving the classroom, please take your rubbish with you and make sure the doors and windows are closed.</t>
+          <t>My phone was broken by my younger brother.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>根据规定，禁止将食物带入图书馆。</t>
+          <t>他的自行车叫人偷走了，这件事由警察来处理。</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>According to the rules, bringing food into the library is prohibited.</t>
+          <t>His bicycle was stolen, and the matter will be handled by the police.</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>这些商品的质量问题应该由工厂负责。</t>
+          <t>他将那封信仔细地看了一遍。</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>The quality issues with these goods should be the factory's responsibility.</t>
+          <t>He carefully read through that letter.</t>
         </is>
       </c>
     </row>
@@ -16355,12 +16360,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>作为首都，北京的发展比一般的城市更快，工作机会更多。</t>
+          <t>按照学校的规定，上课期间不能使用手机。</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>As the capital, Beijing develops faster than ordinary cities and offers more job opportunities.</t>
+          <t>In accordance with school regulations, mobile phones cannot be used during class.</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -16417,22 +16422,22 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>公司讨论并通过了这项计划。</t>
+          <t>她年轻而有才华，深受大家喜爱。</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>The company discussed and approved this plan.</t>
+          <t>She is young and talented; everyone adores her.</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>这里的朋友们热情而友好。</t>
+          <t>质量与价格同样重要。</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>The friends here are warm and friendly.</t>
+          <t>Quality and price are equally important.</t>
         </is>
       </c>
     </row>
@@ -16469,32 +16474,32 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>我每天要上两节中文课，此外一周还要参加一次文化活动。</t>
+          <t>既然你决定出发，就要坚持到底，不过要注意安全。</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>I have two Chinese lessons every day, and besides that, I attend a cultural activity once a week.</t>
+          <t>Since you have decided to set out, you should see it through — but do pay attention to safety.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>我来中国是想提高自己的汉语水平，此外还想学习中国文化。</t>
+          <t>他表面平静而内心紧张，甚至手都开始抖了。</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>I came to China to improve my Chinese, and in addition I want to learn about Chinese culture.</t>
+          <t>He appeared calm on the surface while feeling nervous inside — his hands had even started shaking.</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>冬天的时候，北方下雪比较多，而南方下雪比较少。</t>
+          <t>这家店价格不贵，此外服务也好，并且位置方便。</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>In winter, the north gets a lot of snow, whereas the south gets relatively little.</t>
+          <t>This shop has reasonable prices; besides that, the service is good, and moreover the location is convenient.</t>
         </is>
       </c>
     </row>
@@ -16531,32 +16536,32 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>我不光要学习中文，还要学习中国的历史和文化。</t>
+          <t>不光他，不仅我们班，全校都参加了。</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>I not only need to study Chinese, but also Chinese history and culture.</t>
+          <t>Not just him — not just our class, but the whole school participated.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>学校周围不光环境好，交通也很方便。</t>
+          <t>加上今天的作业，我已经做了三个小时了。</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>The area around the school not only has a nice environment, but the transportation is also very convenient.</t>
+          <t>Adding today's homework, I have been working for three hours.</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>我弟弟不仅学习成绩好，而且性格也很好。</t>
+          <t>由于下雨，活动因此推迟，另外改到室内举行。</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>My younger brother not only has excellent grades, but also has a great personality.</t>
+          <t>Due to rain, the event was therefore postponed and additionally moved indoors.</t>
         </is>
       </c>
     </row>
@@ -16593,32 +16598,32 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>我会说英语、汉语、法语等很多种语言。</t>
+          <t>北京、上海、广州等大城市的房价都很高。</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>I can speak English, Chinese, French, and many other languages.</t>
+          <t>Housing prices in major cities such as Beijing, Shanghai, Guangzhou, and others are all very high.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>你最好提前上网了解一下那里的天气、交通、景点等方面的信息。</t>
+          <t>学者的责任，在于推动知识之进步。</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>You'd better look up information about the weather, transportation, attractions, and so on there in advance.</t>
+          <t>The responsibility of scholars lies in advancing the progress of knowledge.</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>根据学校的规定，迟到十分钟以上者不允许参加考试。</t>
+          <t>他的优点就是做事认真。</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>According to the school's rules, those who are more than ten minutes late are not allowed to take the exam.</t>
+          <t>His strong point is that he is meticulous in his work.</t>
         </is>
       </c>
     </row>
@@ -16650,46 +16655,32 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>啊，原来是这么一回事！                                          
-啊，这么多人排队！
-A：八点出发来得及吗？
-B：嗯，应该来得及。</t>
+          <t>啊，原来是这么一回事！</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Ah, so that's how it is!
-Oh, so many people in line!
-A: Will leaving at eight be in time?
-B: Mm, it should be.</t>
+          <t>Ah, so that's how it is!</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>啊，我把钥匙忘在家里了！
-A：你明天有空吗？
-B：嗯，没什么事。</t>
+          <t>啊，我把钥匙忘在家里了！</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Oh no, I left my keys at home!
-A: Are you free tomorrow?
-B: Mm, I don't have anything going on.</t>
+          <t>Oh no, I left my keys at home!</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>啊，外面下雪了！
-A：这道菜好吃吗？
-B：嗯，很好吃。</t>
+          <t>嗯，我知道了，你说的有道理。</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>Oh, it's snowing outside!
-A: Is this dish good?
-B: Mm, it's very good.</t>
+          <t>Mm-hmm, I see — what you said makes sense.</t>
         </is>
       </c>
     </row>
@@ -16721,38 +16712,32 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>奶奶把一小盒巧克力装进了孙子的书包里。
-回国前，我给父母买了两大包中国茶作为礼物。</t>
+          <t>奶奶把一小盒巧克力装进了孙子的书包里。</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Grandma put a small box of chocolates into her grandson's schoolbag.
-Before returning home, I bought my parents two large bags of Chinese tea as gifts.</t>
+          <t>Grandma put a small box of chocolates into her grandson's schoolbag.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>他喝了一大杯水才感觉好一点儿。
-她带了一小瓶水去旅行。</t>
+          <t>他喝了一大杯水才感觉好一点儿。</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>He drank a large glass of water before feeling a little better.
-She brought a small bottle of water on her trip.</t>
+          <t>He drank a large glass of water before feeling a little better.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>桌子上放着三大碗米饭。
-孩子书包里有一小本笔记本。</t>
+          <t>桌子上放着三大碗米饭。</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>Three large bowls of rice were placed on the table.
-The child had a small notebook in their schoolbag.</t>
+          <t>Three large bowls of rice were placed on the table.</t>
         </is>
       </c>
     </row>
@@ -16871,12 +16856,12 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>他生活无苦无难，每天都很快乐。</t>
+          <t>他整天无忧无虑，很快乐。</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>He lives free of hardship and trouble, happy every day.</t>
+          <t>He is carefree all day and very happy.</t>
         </is>
       </c>
     </row>
@@ -16923,22 +16908,22 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>这部作品的人物都写得有血有肉。</t>
+          <t>她做事有条有理，大家都很信任她。</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Every character in this work is written with flesh and blood — vivid and fully realized.</t>
+          <t>She does things in an orderly way; everyone trusts her.</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>他说的话有理有据，大家都信服了。</t>
+          <t>这个地方有山有水，风景很美。</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>What he said was well-reasoned and well-supported, and everyone was convinced.</t>
+          <t>This place has mountains and water — the scenery is beautiful.</t>
         </is>
       </c>
     </row>
@@ -16975,42 +16960,32 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>我这两天很忙，没来得及考虑这个问题。                                   
-我想参加明天的比赛，现在报名来得及吗？
-我发现这个问题时已经太晚了，来不及改变什么。
-飞机就要起飞了，你得快一点儿，否则就来不及了。</t>
+          <t>我想参加明天的比赛，现在报名来得及吗？</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>I've been very busy these past two days and haven't had time to think about this issue.
-I'd like to enter tomorrow's competition — is it still possible to register now?
-By the time I noticed the problem it was already too late to change anything.
-The plane is about to take off — you need to hurry, otherwise you won't make it.</t>
+          <t>I'd like to enter tomorrow's competition — is it still possible to register now?</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>他接到通知就出发了，还来得及赶上会议。
-火车五分钟后就开了，我们来不及买东西了。</t>
+          <t>火车五分钟后就开了，我们来不及买东西了。</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>He set off as soon as he got the notice, and still made it to the meeting in time.
-The train leaves in five minutes — we no longer have time to buy anything.</t>
+          <t>The train leaves in five minutes — we no longer have time to buy anything.</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>你现在去换衣服还来得及。
-他跑得太慢，来不及追上那辆公共汽车。</t>
+          <t>你现在去换衣服还来得及。</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>There's still time for you to go change your clothes now.
-He ran too slowly and couldn't catch up with the bus in time.</t>
+          <t>There's still time for you to go change your clothes now.</t>
         </is>
       </c>
     </row>
@@ -17047,14 +17022,12 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>一次失败没什么，以后有的是机会。
-这种水果我的家乡有的是。</t>
+          <t>一次失败没什么，以后有的是机会。</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>One failure is nothing — there will be plenty of opportunities ahead.
-This kind of fruit is plentiful back in my hometown.</t>
+          <t>One failure is nothing — there will be plenty of opportunities ahead.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17111,24 +17084,22 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>说不定他今天有事，先等一下吧。
-这件事说不定，再看看再说。</t>
+          <t>说不定他今天有事，先等一下吧。</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Maybe he's busy today — let's wait a moment.
-This matter is hard to say — let's observe a bit more before deciding.</t>
+          <t>Maybe he's busy today — let's wait a moment.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>说不定他今天不来了，你先吃吧。</t>
+          <t>说不定明天会下雨，带上雨伞吧。</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Maybe he's not coming today — go ahead and eat.</t>
+          <t>It might rain tomorrow — bring an umbrella.</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -17175,14 +17146,12 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>她从来都不怎么关心别人的看法。
-从检查结果来看，他受的伤不怎么严重。</t>
+          <t>她从来都不怎么关心别人的看法。</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>She has never really cared much about what others think.
-Judging from the examination results, his injury is not particularly serious.</t>
+          <t>She has never really cared much about what others think.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17239,34 +17208,32 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>他们没有直接拒绝你，而是让你回来等消息，就是说，你还有希望，千万不要放弃。
-他总是为自己的错误找各种原因，这就是说，他是一个不愿意负责任的人。</t>
+          <t>火车票已经卖完了，就是说，我们只能坐汽车去了。</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>They didn't reject you outright — they asked you to come back and wait for news. That is to say, you still have hope, so don't give up.
-He always finds all sorts of excuses for his mistakes — in other words, he's someone who is unwilling to take responsibility.</t>
+          <t>The train tickets are all sold out — that is to say, we can only go by bus.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>火车票已经卖完了，就是说，我们只能坐汽车去了。</t>
+          <t>她一句话也没说就走了，这就是说，她对这件事不满意。</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>The train tickets are all sold out — that is to say, we can only go by bus.</t>
+          <t>She left without saying a word — in other words, she was dissatisfied with the matter.</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>她一句话也没说就走了，这就是说，她对这件事不满意。</t>
+          <t>他总是为自己的错误找各种原因，这就是说，他是一个不愿意负责任的人。</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>She left without saying a word — in other words, she was dissatisfied with the matter.</t>
+          <t>He always finds all sorts of excuses for his mistakes — in other words, he's someone who is unwilling to take responsibility.</t>
         </is>
       </c>
     </row>
@@ -17407,12 +17374,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>你男朋友真够浪漫的，每天都给你送一枝花。</t>
+          <t>你男朋友真够浪漫的，每天都给你送花。</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Your boyfriend is really quite romantic — he brings you a flower every single day.</t>
+          <t>Your boyfriend is really quite romantic — he brings you flowers every single day.</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -17563,12 +17530,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>每天都细心照顾，可窗台上的花怎么都不开。</t>
+          <t>每天都细心照顾，可家里的花怎么都不开。</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Despite careful tending every day, the flowers on the windowsill just won't bloom.</t>
+          <t>Despite careful tending every day, the flowers at home just won't bloom.</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -17615,12 +17582,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>我们减少使用塑料袋，是为了保护环境而改变习惯。</t>
+          <t>我们为了保护环境而改变了生活习惯。</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>We are reducing our use of plastic bags — changing our habits in order to protect the environment.</t>
+          <t>We changed our lifestyle habits for the sake of protecting the environment.</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -17657,12 +17624,12 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>虽然日子过得很难，但也不能过一天是一天。</t>
+          <t>他做事一步是一步，很有计划。</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Even though life is hard, you can't just muddle through one day at a time.</t>
+          <t>He does things step by step; very methodical.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17870,17 +17837,17 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Stop wasting time — just say whatever's on your mind.</t>
+          <t>Stop wasting time — just say whatever is on your mind.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>你不要生气，下次別答应他就是了。</t>
+          <t>下次别答应他就是了。</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Don't be angry — next time just don't agree to it, simple as that.</t>
+          <t>Just do not agree to it next time.</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -17890,7 +17857,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>If you don't want to go, just say so directly — no need to overthink it.</t>
+          <t>If you do not want to go, just say so directly — no need to overthink it.</t>
         </is>
       </c>
     </row>
@@ -17937,12 +17904,12 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>还说自己会做饭呢，连鸡蛋都炒糊了。</t>
+          <t>还说自己会做饭呢，饭都做糊了。</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>Claimed they could cook — and then burned even the scrambled eggs.</t>
+          <t>Claimed they could cook — and then even burned the rice.</t>
         </is>
       </c>
     </row>
@@ -18041,12 +18008,12 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>让你休息你就休息，别硬撑着。</t>
+          <t>让你早点睡你就早点睡，对身体好。</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>If they're telling you to rest, then just rest — don't force yourself to keep going.</t>
+          <t>If they're telling you to sleep early, just sleep early — it's good for your health.</t>
         </is>
       </c>
     </row>
@@ -18078,7 +18045,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>He's been injured — I absolutely must go and see him, no matter what.</t>
+          <t>He has been injured — I absolutely must go and see him, no matter what.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18088,17 +18055,17 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>We're about to be late — we really have to go now, no excuses.</t>
+          <t>We are about to be late — we really have to go now, no excuses.</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>这么有用的技术，我怎么（着）也得学。</t>
+          <t>这么有用的技术，我怎么着也得学。</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>This technology is so useful — I absolutely have to learn it, no matter what it takes.</t>
+          <t>This technology is so useful; I absolutely must learn it.</t>
         </is>
       </c>
     </row>
@@ -18125,22 +18092,22 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>买就买（点儿）吧，也不太贵。</t>
+          <t>买就买点儿吧，别买太多。</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Well, if we're going to buy some, let's just buy some — it's not that expensive anyway.</t>
+          <t>If you are buying, just buy a little — do not buy too much.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>慢就慢（点儿）吧，能做完就行。</t>
+          <t>慢就慢点儿吧，安全最重要。</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>If it takes a bit longer, so be it — as long as it gets done.</t>
+          <t>If it is slow, then let it be slow — safety is most important.</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -18150,7 +18117,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>If it's a bit far, so be it — as long as the environment is nice, it's worth it.</t>
+          <t>If it is a bit far, so be it — as long as the environment is nice, it is worth it.</t>
         </is>
       </c>
     </row>
@@ -18234,42 +18201,32 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>面试的时候，我心里紧张死了。
-不知道从哪儿来的声音，吵死了。
-吃完冰激凌，我突然牙疼得厉害。
-我们这儿有个同学病得很厉害，请你们赶快来看看。</t>
+          <t>面试的时候，我心里紧张死了。</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>During the interview, I was terribly nervous inside.
-I don't know where that sound is coming from — it's incredibly noisy.
-After eating the ice cream, I suddenly had a really bad toothache.
-One of the students here is seriously ill — please come quickly to take a look.</t>
+          <t>During the interview, I was terribly nervous inside.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>今天走了这么多路，我的脚疼死了。
-这道题太难了，我烦死了。</t>
+          <t>今天走了这么多路，我的脚疼死了。</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>I've walked so much today — my feet are killing me.
-This problem is too hard — I'm incredibly frustrated.</t>
+          <t>I've walked so much today — my feet are killing me.</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>他头疼得厉害，早早就回家休息了。
-外面的音乐太吵，我困死了却睡不着。</t>
+          <t>他头疼得厉害，早早就回家休息了。</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>He had a terrible headache and went home early to rest.
-The music outside was so loud — I was dead tired but couldn't sleep.</t>
+          <t>He had a terrible headache and went home early to rest.</t>
         </is>
       </c>
     </row>
@@ -18301,42 +18258,32 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>你点了这么多菜，我们两个吃得了吗？
-我帮你一起做，下班之前肯定完成得了。
-行李太重了，我拿不了。
-明天的比赛他参加不了。</t>
+          <t>行李太重了，我拿不了。</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>You've ordered so much food — can just the two of us finish it?
-I'll help you do it — we can definitely finish it before we get off work.
-The luggage is too heavy — I can't carry it.
-He won't be able to participate in tomorrow's competition.</t>
+          <t>The luggage is too heavy — I can't carry it.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>这本书太厚了，今天看不了。
-就你一个人，这些工作做得了吗？</t>
+          <t>这么多东西，你一个人拿得了吗？</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>This book is too thick — I can't finish reading it today.
-With just you alone, can all this work actually get done?</t>
+          <t>Can you carry this much stuff by yourself?</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>他受伤了，这次旅游去不了了。
-你放心，这点儿小事我自己办得了。</t>
+          <t>他受伤了，这次旅游去不了了。</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>He was injured and won't be able to go on this trip.
-Don't worry — I can handle this small matter myself.</t>
+          <t>He was injured and won't be able to go on this trip.</t>
         </is>
       </c>
     </row>
@@ -18703,12 +18650,12 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>他把椅子往前移了移。</t>
+          <t>他把椅子往前推了推。</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>He moved the chair forward a little.</t>
+          <t>He pushed the chair forward a little.</t>
         </is>
       </c>
     </row>
@@ -18755,12 +18702,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>相机叫谁拿走了？</t>
+          <t>他的自行车叫人偷走了，很心疼。</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Who took the camera?</t>
+          <t>His bicycle was stolen by someone; he is heartbroken.</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -19447,12 +19394,12 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>做菜的时候，首先把菜洗干净，然后再开始切。</t>
+          <t>考试前，首先把材料准备好，然后再认真复习。</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>When cooking, first wash the vegetables clean, then start cutting them.</t>
+          <t>Before an exam, first get your materials ready, then review carefully.</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19523,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>He studies very hard, reviewing late every day — he even doesn't take a break on weekends.</t>
+          <t>He studies very hard, reviewing late every day — he doesn't even take a break on weekends.</t>
         </is>
       </c>
     </row>
@@ -20687,12 +20634,12 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>就是路再远，他也要去看望老师。</t>
+          <t>就是路再远，他也要去见老师。</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>Even if the road is very long, he still wants to go visit his teacher.</t>
+          <t>Even if the road is very long, he still wants to go see his teacher.</t>
         </is>
       </c>
     </row>
@@ -20848,12 +20795,12 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>这栋楼里住着三百来户人家。</t>
+          <t>教室里坐了五十来个学生。</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Around three hundred households live in this building.</t>
+          <t>Around fifty students are sitting in the classroom.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -20873,7 +20820,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>This big fish is estimated to weigh around ten jin.</t>
+          <t>This big fish is estimated to weigh around ten jin (about 5 kg).</t>
         </is>
       </c>
     </row>
@@ -20962,32 +20909,32 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>零点五、三分之一、百分之二十、两倍</t>
+          <t>这件商品打了九折，也就是零点九。</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>0.5, one-third, 20%, twice (double)</t>
+          <t>This item is at a nine-tenths discount — in other words, multiplied by 0.9.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>老师听写了二十个汉字，每个汉字零点五分，一共十分。</t>
+          <t>这个城市的人口是去年的两倍。</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>The teacher dictated twenty Chinese characters; each character was worth 0.5 points, for a total of 10 points.</t>
+          <t>This city's population is twice what it was last year.</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>我们班有三分之一的同学没去过长城。</t>
+          <t>这次考试，百分之九十的学生通过了，只有三分之一的人得了满分。</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>One-third of the students in our class have never been to the Great Wall.</t>
+          <t>Ninety percent of the students passed this exam, but only one-third of them got a perfect score.</t>
         </is>
       </c>
     </row>
@@ -21019,14 +20966,12 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>那块石头上刻着一些汉字。
-那本书里头是不是有一封信？</t>
+          <t>那块石头上刻着一些汉字。</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Some Chinese characters are carved on that stone.
-Is there a letter inside that book?</t>
+          <t>Some Chinese characters are carved on that rock.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21093,12 +21038,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>他们已经认识很久了，对彼此的习惯非常了解。</t>
+          <t>本公司的产品质量有保证。</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>They have known each other for a long time and are very familiar with each other's habits.</t>
+          <t>The quality of this company's products is guaranteed.</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -21145,32 +21090,32 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>这册历史书讲述了古代中国的发展过程。</t>
+          <t>图书馆又买了三十册新书，书架上整整齐齐。</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>This volume of history books describes the development of ancient China.</t>
+          <t>The library bought 30 more volumes; the shelves are neatly arranged.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>第一次见面时他送给了我一朵玫瑰花。</t>
+          <t>花园里开满了一朵朵红花，一群蜜蜂在飞舞。</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>The first time we met, he gave me a rose.</t>
+          <t>The garden is filled with red flowers; a swarm of bees is flying about.</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>这届会议讨论了许多重要的话题。</t>
+          <t>他递给我一支笔和一副眼镜。</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>This session of the conference discussed many important topics.</t>
+          <t>He handed me a pen and a pair of glasses.</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21162,7 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>他往窗外瞧了一眼，发现外面下起了大雨。</t>
+          <t>他往窗外看了一眼，发现外面下起了大雨。</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
@@ -21269,32 +21214,32 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>他在面试时过于紧张，连话都说不清楚了。</t>
+          <t>他说话过于直接，格外让人感到不舒服。</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>He was excessively nervous during the interview — he couldn't even speak clearly.</t>
+          <t>He speaks excessively bluntly, which is particularly off-putting.</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>过于追求完美反而会让人总是对现状不满意。</t>
+          <t>这位演员的表演相当出色，极其投入。</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Being excessively perfectionistic actually causes people to always be dissatisfied with the way things are.</t>
+          <t>This actor's performance is quite outstanding and extremely devoted.</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>这次考试的题目相当难，很多同学都没有及格。</t>
+          <t>这种方法较那种更有效，效果可好了，可以节省不少时间。</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>The questions on this exam were quite difficult — many students did not pass.</t>
+          <t>This method is relatively more effective than that one — it really works well and can save quite a bit of time.</t>
         </is>
       </c>
     </row>
@@ -21331,32 +21276,32 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>父母要时刻关心孩子的心理健康。</t>
+          <t>他始终坚持锻炼，早晚各跑一次。</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Parents should always pay attention to their children's mental health.</t>
+          <t>He always sticks to exercising — a run in the morning and evening.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>他提醒我旅行时一定要时刻注意自己的护照和钱包。</t>
+          <t>即将毕业，大家早已开始找工作了。</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>He reminded me to always keep an eye on my passport and wallet when traveling.</t>
+          <t>Graduation is approaching; everyone has long since started job hunting.</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>她曾经当过导游，在设计旅行线路方面很有经验。</t>
+          <t>他曾经在北京生活过，时刻怀念那段日子。</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>She used to work as a tour guide and has a lot of experience planning travel itineraries.</t>
+          <t>He once lived in Beijing and constantly misses that period of his life.</t>
         </is>
       </c>
     </row>
@@ -21403,22 +21348,22 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>你出门老是忘记带钥匙，这个坏习惯一定要改！</t>
+          <t>旅行社通常在寒暑假生意更好。</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>You keep forgetting to take your keys when you go out — you really need to break that bad habit!</t>
+          <t>Travel agencies usually do better business during winter and summer holidays.</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>旅行社通常在寒暑假生意更好。</t>
+          <t>她时常去图书馆看书，知识面很广。</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>Travel agencies usually do better business during winter and summer holidays.</t>
+          <t>She often goes to the library to read, so she has a broad base of knowledge.</t>
         </is>
       </c>
     </row>
@@ -21641,32 +21586,32 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>毕竟他刚来公司一个月，还需要时间适应。</t>
+          <t>他毕竟是孩子，居然说出这么成熟的话。</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>After all, he has only been with the company for a month — he still needs time to adjust.</t>
+          <t>He's just a child after all — he surprisingly said something so mature.</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>他毕竟是个孩子，有些错误可以被原谅。</t>
+          <t>反正已经来了，果然比想象的好玩多了。</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>He is, after all, just a child — some mistakes can be forgiven.</t>
+          <t>Since we're already here, it turns out it's a lot more fun than expected.</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>昨天我才发现新来的同事居然是我的邻居。</t>
+          <t>他的确刚好路过，根本不是故意的，简直太巧了。</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>Yesterday I discovered that the new colleague who just joined is actually my neighbor — what a surprise.</t>
+          <t>He really did just happen to be passing by — it was absolutely not intentional; it was simply too much of a coincidence.</t>
         </is>
       </c>
     </row>
@@ -21837,22 +21782,22 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>我出差期间，同事替我照顾我的宠物。</t>
+          <t>明天我同他一起去参加那个会议。</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>While I was away on a business trip, my colleague looked after my pet for me.</t>
+          <t>Tomorrow I will attend that meeting together with him.</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>汉语同其他语言一样，有很多独特的表达方式。</t>
+          <t>较上个月，这个月的销量有所提高。</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>Like other languages, Chinese has many unique ways of expressing things.</t>
+          <t>Compared with last month, this month's sales have increased somewhat.</t>
         </is>
       </c>
     </row>
@@ -22137,32 +22082,32 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>学校更新了教学设备，从而为学生提供了更好的学习环境。</t>
+          <t>他三年没回家，可见工作有多忙。</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>The school updated its teaching equipment, thereby providing students with a better learning environment.</t>
+          <t>He hasn't been home in three years — you can see just how busy work is.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>这次合作让我们加深了对彼此的了解，从而建立了深厚的友谊。</t>
+          <t>她坚持练习，从而取得了进步。</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>This collaboration deepened our understanding of each other, thereby building a deep friendship.</t>
+          <t>She persisted in practicing, thereby making progress.</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>他每天都工作到很晚，可见他十分热爱这份工作。</t>
+          <t>假如明天下雨，我们就改在室内开会；总之，活动不会取消。</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>He works until late every day — clearly he is deeply passionate about this job.</t>
+          <t>If it rains tomorrow, we will move the meeting indoors; in short, the event will not be cancelled.</t>
         </is>
       </c>
     </row>
@@ -22405,12 +22350,12 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>他做事没头没脑，经常给别人添麻烦。</t>
+          <t>他做事没头没脑，常常让别人不高兴。</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>He acts without any sense or direction, always causing trouble for others.</t>
+          <t>He acts without any sense and often makes others unhappy.</t>
         </is>
       </c>
     </row>
@@ -22509,14 +22454,12 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>他最近的表现好得不得了，老师都说他进步很大。
-不得了了，厨房着火了！</t>
+          <t>他最近的表现好得不得了，老师都说他进步很大。</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>His performance lately has been incredibly good — even the teacher says he has made great progress.
-Oh no, the kitchen is on fire!</t>
+          <t>His performance lately has been incredibly good — even the teacher says he has made great progress.</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22573,16 +22516,12 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>这点儿小病，用不着去医院。
-这件事用不着大家都来帮忙，我自己就能完成。
-我们还有时间，你现在用不着着急。</t>
+          <t>这点儿小病，用不着去医院。</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>It's just a minor illness — there's no need to go to the hospital.
-There's no need for everyone to come and help with this — I can handle it myself.
-We still have time; there's no need to rush right now.</t>
+          <t>It's just a minor illness — there's no need to go to the hospital.</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22899,22 +22838,22 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>妈妈做的菜太多了，她吃也吃不得，扔也扔不得，只好请邻居来帮忙。</t>
+          <t>这件事说也说不得，做也做不得，真让人为难。</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>Mom made too much food — she couldn't eat it all and couldn't throw it away, so she had to invite the neighbors over to help.</t>
+          <t>This matter can neither be spoken of nor acted upon — it really puts people in a difficult position.</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>这个礼物又大又重，他拿也拿不得，放也放不得，不知道该怎么办。</t>
+          <t>那封信，看也看不得，扔也扔不得，真不知道怎么办。</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>The gift was big and heavy — he couldn't carry it and couldn't put it down, so he had no idea what to do.</t>
+          <t>That letter — you can't bring yourself to look at it, and you can't throw it away; I really don't know what to do.</t>
         </is>
       </c>
     </row>
@@ -22941,22 +22880,22 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>好是它，坏也是它，你没有别的选择。</t>
+          <t>钱，好是它，坏也是它，人生离不开它。</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Whether it goes well or badly, it's all down to this — you have no other choice.</t>
+          <t>Money — when things go well, it's because of it; when things go badly, it's also because of it. You can't escape it in life.</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>成功是它，失败也是它，这个决定我绝对不后悔。</t>
+          <t>成也网络，败也网络，现代人的生活离不开它。</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Whether it leads to success or failure, this is my decision and I have absolutely no regrets.</t>
+          <t>The internet is behind both our successes and our failures — modern people's lives cannot do without it.</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -23045,7 +22984,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>不管怎么说，健康才是最重要的，要注意身体。</t>
+          <t>不管怎样说，健康才是最重要的，要注意身体。</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23055,7 +22994,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>不管怎么说，用打骂的方法教育孩子是不对的。</t>
+          <t>不管怎样说，用打骂的方法教育孩子是不对的。</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
@@ -23065,7 +23004,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>不管怎么说，你已经尽力了，结果并不是最重要的。</t>
+          <t>不管怎样说，你已经尽力了，结果并不是最重要的。</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -23486,12 +23425,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>他是否可以出院，得先问问医生的意见。</t>
+          <t>这件事你做不得，会出大问题的。</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Whether he can be discharged from the hospital or not, you need to ask the doctor's opinion first.</t>
+          <t>You can't do this — it will cause serious problems.</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -23600,32 +23539,32 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>听着窗外的雨声，我的心慢慢地平静下来了。</t>
+          <t>天气渐渐冷下来了。</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Listening to the rain outside the window, my heart gradually calmed down.</t>
+          <t>The weather is gradually getting colder.</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>不知道是什么原因，他的声音渐渐低了下去。</t>
+          <t>只要你坚持下去，一定会成功的。</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>For some reason, his voice gradually trailed off lower and lower.</t>
+          <t>As long as you keep going, you will definitely succeed.</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>该睡觉了，快把你的玩具收拾起来。</t>
+          <t>听到好消息，他高兴地笑起来了。</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>It's time for bed — hurry up and put your toys away.</t>
+          <t>Hearing the good news, he started to laugh happily.</t>
         </is>
       </c>
     </row>
@@ -24034,22 +23973,22 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>他把存款都买车了。</t>
+          <t>他把时间都花在看书上了。</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>He spent all his savings on a car.</t>
+          <t>He spent all his time reading.</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>我把父母给的生活费借朋友了。</t>
+          <t>我把父母给的生活费借给朋友了。</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>I lent my friend the living allowance my parents gave me.</t>
+          <t>I lent the living expenses my parents gave me to a friend.</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -24096,32 +24035,32 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>她丈夫生病住院了。（因果）</t>
+          <t>他努力学习，终于考上了大学。</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Her husband fell ill and was hospitalized. (causal)</t>
+          <t>He studied hard and finally got into university.</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>王经理去开会忘了带资料。（转折）</t>
+          <t>王经理去开会忘了带资料。</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Manager Wang went to the meeting but forgot to bring the materials. (adversative)</t>
+          <t>Manager Wang went to the meeting but forgot to bring the materials.</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>面对快速变化的形势，我们应该尽快制定方案应对风险。（条件）</t>
+          <t>你努力工作，就会得到回报。</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>Facing a rapidly changing situation, we should draw up a plan as soon as possible to address the risks. (conditional)</t>
+          <t>If you work hard, you will get rewarded.</t>
         </is>
       </c>
     </row>
@@ -24344,12 +24283,12 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>晚餐我或是吃面条儿，或是喝粥。</t>
+          <t>晚餐我或是吃面条儿，或是吃饺子。</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>For dinner I'll either have noodles or congee.</t>
+          <t>For dinner I'll either have noodles or dumplings.</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24674,12 +24613,12 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>他缺乏经验，因而在处理问题时常常犯错。</t>
+          <t>他缺乏经验，因而在处理问题时常常出错。</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>He lacks experience, and as a result he often makes mistakes when dealing with problems.</t>
+          <t>He lacks experience, and as a result he often makes errors when dealing with problems.</t>
         </is>
       </c>
     </row>
@@ -24840,12 +24779,12 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>他不但不改正错误，反而继续犯更大的错误。</t>
+          <t>他不但不改正，错误反而越来越多。</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Not only did he fail to correct his mistakes, he went on to make even bigger ones.</t>
+          <t>Not only did he not correct his mistakes, they actually kept getting worse.</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -24860,12 +24799,12 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>火不但没有灭，反而越来越大了。</t>
+          <t>火不但没有停，反而越来越大了。</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>The fire not only failed to go out — it actually grew bigger and bigger.</t>
+          <t>The fire not only didn't stop — it actually grew bigger and bigger.</t>
         </is>
       </c>
     </row>
@@ -24912,12 +24851,12 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>这个问题不是我一个人就能解决的，还是需要大家积极配合。</t>
+          <t>学好外语不是一朝一夕的事，还需要长期坚持。</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>This problem is not something I can solve on my own — everyone still needs to actively cooperate.</t>
+          <t>Mastering a foreign language is not something done overnight; it also requires long-term perseverance.</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -25207,56 +25146,32 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>没想到他竟然超水平发挥，最终赢得了这场比赛。
-这位演员的表演总能展现出多层次的人物心理。
-父母过分关注孩子的每个动作，会对孩子的成长起到反作用。
-公司所有电脑系统都经过了严格的安全检查，确保无病毒运行。
-新开发的商业区已经成为了城市亚中心，发展潜力巨大。
-小张和女朋友小李已经订婚了，小李现在是张家的准媳妇。</t>
+          <t>这款超轻材料多功能，广泛用于建筑。</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Nobody expected him to perform above his level and ultimately win the match.
-This actor's performances always reveal multi-layered inner psychology.
-Parents who pay excessive attention to their child's every move can have a counter-productive effect on the child's development.
-All of the company's computer systems underwent rigorous security checks to ensure they run virus-free.
-The newly developed commercial district has become a sub-center of the city, with enormous development potential.
-Xiao Zhang and his girlfriend Xiao Li are engaged — Xiao Li is now the future daughter-in-law of the Zhang family.</t>
+          <t>This ultra-light, multi-function material is widely used in construction.</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>这款手机的超高清屏幕让图像看起来非常清晰。
-这项研究是一个多学科合作的项目，涉及医学、心理学和社会学。
-他的表现完全反常，让大家都感到担心。
-这款饮料声称无添加，深受注重健康的消费者欢迎。
-这个小城市属于亚热带地区，冬天不太冷。
-她是我准姐夫的妹妹，下个月就要嫁给我哥了。</t>
+          <t>他的反社会行为让无数人感到反感。</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>The ultra-high-definition screen on this phone makes images look extremely sharp.
-This research is a multi-disciplinary collaborative project involving medicine, psychology, and sociology.
-His behavior was completely counter to his usual self, which worried everyone.
-This beverage claims to be additive-free and is popular among health-conscious consumers.
-This small city belongs to the subtropical zone — winters there are not very cold.
-She is my future brother-in-law's sister; she and my brother are getting married next month.</t>
+          <t>His anti-social behavior made countless people feel repulsed.</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>这个小区是无障碍设计，方便轮椅使用者出行。
-这位学者是多产型作家，每年都出版好几本书。
-这家公司的反腐行动得到了员工的一致认可。</t>
+          <t>这位亚裔学者被评为准教授。</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>This residential complex is barrier-free by design, making it accessible for wheelchair users.
-This scholar is a prolific writer who publishes several books every year.
-The company's anti-corruption campaign received unanimous approval from employees.</t>
+          <t>This Asian scholar has been appointed associate professor.</t>
         </is>
       </c>
     </row>
@@ -25288,48 +25203,32 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>随着科技的发展，人们迎来了数字化时代。
-本课程采用专题式的教学方法，每课介绍一个专题。
-这种鱼是观赏型的，很多人把它们当做宠物。
-这款产品具备很好的便捷性，使用十分方便。</t>
+          <t>工厂的生产已经全面自动化了。</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>With the development of technology, people have entered the digital age.
-This course adopts a thematic teaching method, with each lesson introducing one topic.
-This type of fish is ornamental, and many people keep them as pets.
-This product has excellent convenience — it is very easy to use.</t>
+          <t>The factory's production has been fully automated.</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>城市绿化工作做得越来越好，公园和草地越来越多。
-他们举办了一场西式婚礼，现场充满了浪漫的气氛。
-她是管理型的人才，特别擅长组织和协调工作。
-学好外语需要长期坚持，重要的是培养语言的敏感性。</t>
+          <t>这道菜是中式做法，用了很多香料。</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>Urban greening efforts are improving steadily, with more and more parks and lawns appearing.
-They held a Western-style wedding, and the venue was filled with a romantic atmosphere.
-She is a management-type talent, particularly skilled at organizing and coordinating work.
-Mastering a foreign language requires long-term persistence; what matters most is developing sensitivity to the language.</t>
+          <t>This dish is cooked in Chinese style and uses many spices.</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>工厂引进了自动化设备，大大提高了生产效率。
-这款桌椅可以收起来，不用时能节省很多空间。
-做科研需要严肃性，每一个数据都要认真检查。</t>
+          <t>这款新能源车属于轻型车，其环保性也得到了认可。</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>The factory introduced automated equipment, greatly improving production efficiency.
-This desk and chair set can be folded away — when not in use, it saves a lot of space.
-Doing research requires seriousness; every data point must be carefully checked.</t>
+          <t>This new-energy vehicle belongs to the light-duty type, and its environmental quality has also been recognized.</t>
         </is>
       </c>
     </row>
@@ -25438,22 +25337,22 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>你试试往碗里加几滴醋，说不定味道会更好。</t>
+          <t>他拿着一卷宣纸，打开了一扇木门。</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Try adding a few drops of vinegar to the bowl — it might taste even better.</t>
+          <t>He carried a roll of rice paper and opened a wooden door.</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>下班回家的路上，妈妈买了几枝玫瑰花。</t>
+          <t>他送给我几枝鲜花，花瓣上还挂着几滴露水。</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>On the way home from work, Mom bought a few stems of roses.</t>
+          <t>He gave me a few stems of fresh flowers, with a few drops of dew still clinging to the petals.</t>
         </is>
       </c>
     </row>
@@ -25562,22 +25461,22 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>相声是一种幽默的艺术，特有意思。</t>
+          <t>改进后的仪器操作异常便捷。</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>Cross-talk is a kind of humorous art form — it's really entertaining.</t>
+          <t>After the improvements, the instrument is extraordinarily easy to operate.</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>改进后的仪器操作异常便捷。</t>
+          <t>这道题较为复杂，需要多花一些时间思考。</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>After the improvements, the instrument is extraordinarily easy to operate.</t>
+          <t>This question is comparatively complex and requires spending a bit more time thinking it through.</t>
         </is>
       </c>
     </row>
@@ -25624,22 +25523,22 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>那位老师的书房里净是外文书。</t>
+          <t>我明天在大厅等你，咱们一同出发。</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>That teacher's study is filled with nothing but foreign language books.</t>
+          <t>I'll wait for you in the lobby tomorrow and we can set off together.</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>我明天在大厅等你，咱们一同出发。</t>
+          <t>来参加这次活动的人大都是年轻人。</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>I'll wait for you in the lobby tomorrow and we can set off together.</t>
+          <t>Most of the people who came to this event were young people.</t>
         </is>
       </c>
     </row>
@@ -25676,32 +25575,32 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>他一时紧张，忘记要说什么了。</t>
+          <t>他一时找不到答案，但依旧没有放弃。</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>He got momentarily nervous and forgot what he was going to say.</t>
+          <t>He couldn't find the answer for a moment, but still didn't give up.</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>面对眼前的比赛结果，人们一时难以接受。</t>
+          <t>他仍旧保持一向认真的工作态度。</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>Faced with the result of the match right in front of them, people found it hard to accept at first.</t>
+          <t>He still maintains his consistently meticulous work attitude.</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>她不时看看手机，等待着朋友的消息。</t>
+          <t>不时地，他停下来思考下一步怎么做。</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>She glanced at her phone from time to time, waiting for a message from her friend.</t>
+          <t>Every now and then he would stop and think about what to do next.</t>
         </is>
       </c>
     </row>
@@ -25810,22 +25709,22 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>听完她的演讲，大家不禁鼓起掌来。</t>
+          <t>他特地从外地赶来参加婚礼，赶忙换好衣服就进了会场。</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>After listening to her speech, the audience couldn't help but break into applause.</t>
+          <t>He came specially from out of town for the wedding, hurriedly changed his clothes, and went straight into the venue.</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>上课铃一响，学生们就赶忙跑回了教室。</t>
+          <t>她特意绕路来接我，还偷偷给我准备了礼物。</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>The moment the class bell rang, the students hurried back to the classroom.</t>
+          <t>She deliberately went out of her way to pick me up and secretly prepared a gift for me.</t>
         </is>
       </c>
     </row>
@@ -25872,12 +25771,12 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>有钱就一定会幸福吗？那也未必。</t>
+          <t>有钱的人未必就过得幸福。</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>Does having money necessarily mean happiness? Not necessarily.</t>
+          <t>People who have money do not necessarily live happily.</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -25924,32 +25823,32 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>婚礼那天恰好是新娘的生日。</t>
+          <t>我去找他，恰好他也在找我。</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>The wedding day happened to fall on the bride's birthday.</t>
+          <t>I went looking for him — it just so happened he was looking for me too.</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>下周六我恰好有时间，咱们可以一起去爬山。</t>
+          <t>她明明知道答案，倒是不肯说。</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>I happen to be free next Saturday — we could go hiking together.</t>
+          <t>She clearly knows the answer but just won't say it.</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>你计划得倒是很好，可是你能做到吗？</t>
+          <t>等了半天，总算来了，干脆一起出发吧。</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>Your plan sounds good enough, but can you actually pull it off?</t>
+          <t>After waiting so long, they're finally here — let's just all leave together.</t>
         </is>
       </c>
     </row>
@@ -26606,14 +26505,12 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>我好不容易才获得这次面试机会，一定不会轻易放弃。
-假期好不容易可以休息一下，你怎么还要去公司加班？</t>
+          <t>我好不容易才获得这次面试机会，一定不会轻易放弃。</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>I worked so hard to get this interview opportunity — there's no way I'm giving it up easily.
-The holiday is finally a chance to get some rest — why on earth are you going into the office to work overtime?</t>
+          <t>I worked so hard to get this interview opportunity — there's no way I'm giving it up easily.</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26670,34 +26567,32 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>假如去那家公司工作能为你提供更多的发展空间，那倒也是个不错的选择。
-要是你能从失败中吸取教训，那倒也是件值得高兴的事。</t>
+          <t>假如去那家公司工作能为你提供更多的发展空间，那倒也是个不错的选择。</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>If working at that company would give you more room to grow, that's actually not a bad choice.
-If you can learn from your failure, that's actually something worth being happy about.</t>
+          <t>If working at that company would give you more room to grow, that's actually not a bad choice.</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>A：与其打车，不如骑自行车，还能锻炼身体。B：那倒也是。</t>
+          <t>你说她不太擅长做饭，那倒也是，她更喜欢点外卖。</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>A: Instead of taking a taxi, why not ride a bike? You'd get some exercise too. B: Well, that's actually a fair point.</t>
+          <t>You say she's not great at cooking — that's true enough; she prefers ordering takeout.</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>A：这件事先跟他商量一下比较好。B：那倒是，我差点儿忘了问他。</t>
+          <t>这个地方远是远，那倒是个好去处。</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>A: It would be better to check with him first. B: That's true — I almost forgot to ask him.</t>
+          <t>This place is far, that's true, but it's really a great destination.</t>
         </is>
       </c>
     </row>
@@ -26734,14 +26629,12 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>这些旧衣服扔掉算了，反正也不会再穿了。
-雪下得这么大，估计不会有客人来了，干脆早点儿关门算了。</t>
+          <t>这些旧衣服扔掉算了，反正也不会再穿了。</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Just throw out those old clothes — you're never going to wear them again anyway.
-With snow this heavy, there probably won't be any customers coming. Let's just close up early and call it a day.</t>
+          <t>Just throw out those old clothes — you're never going to wear them again anyway.</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -26798,14 +26691,12 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>得了，别再想了，结果不可能改变了。
-你这么喜欢这本书，干脆送给你得了。</t>
+          <t>得了，别再想了，结果不可能改变了。</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Alright, stop dwelling on it — the outcome can't be changed.
-You like this book so much — just take it, it's yours.</t>
+          <t>Alright, stop dwelling on it — the outcome can't be changed.</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -26852,12 +26743,12 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>我们左一句、右一句地安慰，她才终于不哭了。</t>
+          <t>你一句、我一句，两个人说了很久的话。</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>We consoled her with one reassuring word after another, and she finally stopped crying.</t>
+          <t>Back and forth, the two talked for a long time.</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27476,22 +27367,22 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>我跟你开玩笑呢！看你吓的！</t>
+          <t>看你吓的，我只是开个玩笑。</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>I was just joking! Look how scared you got!</t>
+          <t>Look how scared you got — I was only joking.</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>不就是得了奖学金吗？瞧他得意的！</t>
+          <t>瞧他得意的，不过是考了个第一名而已。</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>It's just a scholarship — look how smug he is about it!</t>
+          <t>Look how smug he is — he only came first in one exam.</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
@@ -27662,32 +27553,32 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>孩子把妈妈气得睡不着觉。</t>
+          <t>他把客人请进了屋里。</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>The child made his mother so angry she couldn't sleep.</t>
+          <t>He ushered the guests inside.</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>她讲述的故事把大家感动哭了。</t>
+          <t>老师把学生叫到了办公室。</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>The story she told moved everyone to tears.</t>
+          <t>The teacher had the student come to the office.</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>这个消息把他高兴得跳起来了。</t>
+          <t>她把孩子送回了家。</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>The news made him so happy he jumped for joy.</t>
+          <t>She sent the child home.</t>
         </is>
       </c>
     </row>

--- a/data/grammar.xlsx
+++ b/data/grammar.xlsx
@@ -4862,22 +4862,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>你试试这双鞋，看合不合脚。</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Try on these shoes and see if they fit.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>你说一说，为什么选这个答案。</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Tell us a bit about why you chose this answer.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>他想了想，最后同意了。</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>He thought it over and finally agreed.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>作业做完了，他也学会了这个词的用法。</t>
+          <t>老师讲的话，我都听懂了。</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>The homework is done, and he has also learned how to use this word.</t>
+          <t>I understood everything the teacher said.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -9650,22 +9650,22 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
+          <t>这么晚了，该睡觉了。</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>It's so late — it's time to sleep.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
           <t>你应该多喝水，注意身体。</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="J153" t="inlineStr">
         <is>
           <t>You should drink more water and take care of your health.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>他不愿意去，我们也不能强迫他。</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>He's unwilling to go; we can't force him.</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>等了很久，车终于来了，他才上车。</t>
+          <t>这本书就三十块钱，很便宜。</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>After waiting a long time, the bus finally came and he got on.</t>
+          <t>This book is only thirty yuan — very cheap.</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>That tall man in front wearing a blue shirt with short hair is my Chinese teacher.</t>
+          <t>That tall man in front wearing blue clothes with short hair is my Chinese teacher.</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>我的自行车让朋友骑走了。</t>
+          <t>她终于考上了大学。</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>My bicycle was taken away by a friend.</t>
+          <t>She finally got into university.</t>
         </is>
       </c>
     </row>
@@ -13585,12 +13585,12 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>妈妈把衣服洗干净了。</t>
+          <t>她把房间打扫得很干净。</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Mom washed the clothes clean.</t>
+          <t>She cleaned the room very thoroughly.</t>
         </is>
       </c>
     </row>
@@ -14081,12 +14081,12 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>你今天比昨天少喝了一杯咖啡。</t>
+          <t>她比我晚到了十分钟。</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>You drank one fewer cup of coffee today than yesterday.</t>
+          <t>She arrived ten minutes later than me.</t>
         </is>
       </c>
     </row>
@@ -15678,22 +15678,22 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>光学语法是不够的，还要多说。</t>
+          <t>光学语法是不够的，还要多说，至少要每天练习口语。</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Just studying grammar is not enough — you also need to speak more.</t>
+          <t>Just studying grammar is not enough — you need to speak more too; at least practice speaking every day.</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>这件事仅仅花了他十分钟，至少比我快多了。</t>
+          <t>全班仅有三人没来；这道题仅仅用了他两分钟。</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>This matter took him only ten minutes — at least much faster than me.</t>
+          <t>Only three students in the whole class were absent; this problem took him only two minutes.</t>
         </is>
       </c>
     </row>
@@ -15802,12 +15802,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>其实，一些看起来很小的事情往往会影响人的一生，偶尔反思一下很有必要。</t>
+          <t>小事往往影响大局，偶尔反思很有必要。</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>In fact, things that seem trivial often end up affecting a person's entire life — it's worthwhile to reflect from time to time.</t>
+          <t>Small things often affect the big picture — occasional reflection is necessary.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -17228,12 +17228,12 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>他总是为自己的错误找各种原因，这就是说，他是一个不愿意负责任的人。</t>
+          <t>他总找借口，这就是说他不愿负责任。</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>He always finds all sorts of excuses for his mistakes — in other words, he's someone who is unwilling to take responsibility.</t>
+          <t>He always makes excuses — in other words, he's unwilling to take responsibility.</t>
         </is>
       </c>
     </row>
@@ -19312,12 +19312,12 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>选择职业的时候，应该首先了解自己的性格、能力，其次再考虑工资、收入等方面的问题。</t>
+          <t>选择职业，首先要了解自己，其次再考虑收入。</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>When choosing a career, you should first understand your own personality and abilities, and then consider issues such as salary and income.</t>
+          <t>When choosing a career, first understand yourself, then consider income.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19384,12 +19384,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>校长首先对同学们表示欢迎，然后介绍了学校的一些基本情况。</t>
+          <t>校长首先表示欢迎，然后介绍了学校情况。</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>The principal first welcomed the students and then gave an introduction to the school's basic situation.</t>
+          <t>The principal first extended a welcome, then introduced the school's situation.</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -19498,12 +19498,12 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>为了锻炼身体，我一有空就去健身房，甚至专门请了一个健身教练。</t>
+          <t>我经常去健身房，甚至还请了健身教练。</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>To get fit, I go to the gym whenever I have free time — I even hired a personal trainer.</t>
+          <t>I go to the gym regularly — I even hired a personal trainer.</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19632,12 +19632,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>随着经济的发展，人们的生活水平提高了，并且对健康和生活质量的要求也越来越高。</t>
+          <t>人们生活水平提高了，并且对健康的要求也越来越高。</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>With economic development, people's living standards have improved, and furthermore their expectations for health and quality of life have grown ever higher.</t>
+          <t>People's living standards have improved, and furthermore their expectations for health have grown ever higher.</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>This item is at a nine-tenths discount — in other words, multiplied by 0.9.</t>
+          <t>This item is at a nine-tenths discount — that is, 0.9.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -22786,12 +22786,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>公司已经三个月没有发工资了，他走也不是，留也不是，不知道怎么办好。</t>
+          <t>他走也不是，留也不是，不知道怎么办好。</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>The company had gone three months without paying salaries — he didn't know whether to quit or stay, and had no idea what to do.</t>
+          <t>He didn't know whether to quit or stay, and had no idea what to do.</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
@@ -22828,12 +22828,12 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>这个小孩太调皮了，爸爸真的没有办法，骂也骂不得，打也打不得。</t>
+          <t>骂也骂不得，打也打不得，爸爸真的没有办法。</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>This child is so naughty that his father really has no idea what to do — he can't scold him, and he can't hit him.</t>
+          <t>He can't scold him and he can't hit him — his father really has no idea what to do.</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -22885,7 +22885,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Money — when things go well, it's because of it; when things go badly, it's also because of it. You can't escape it in life.</t>
+          <t>Money — when things go well it's because of it, when things go badly it's because of it too; life can't do without it.</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23316,12 +23316,12 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>这是我们两个人的事，不能他决定什么就是什么，我的意见也很重要。</t>
+          <t>他决定什么就是什么，我的意见没人听。</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>This is a matter for both of us — it can't be that whatever he decides goes. My opinion matters too.</t>
+          <t>Whatever he decides goes — nobody listens to my opinion.</t>
         </is>
       </c>
     </row>
@@ -23549,22 +23549,22 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>只要你坚持下去，一定会成功的。</t>
+          <t>他突然晕过去了，大家都吓了一跳。</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>As long as you keep going, you will definitely succeed.</t>
+          <t>He suddenly lost consciousness, and everyone was startled.</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>听到好消息，他高兴地笑起来了。</t>
+          <t>他慢慢地清醒过来了。</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>Hearing the good news, he started to laugh happily.</t>
+          <t>He slowly came back to his senses.</t>
         </is>
       </c>
     </row>
@@ -25337,12 +25337,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>他拿着一卷宣纸，打开了一扇木门。</t>
+          <t>他拍了一卷胶卷，打开了一扇木门。</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>He carried a roll of rice paper and opened a wooden door.</t>
+          <t>He shot a roll of film and opened a wooden door.</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -25947,22 +25947,22 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>刚来中国时，我既听不懂也说不清楚，至于写作和阅读，就更不行了。</t>
+          <t>我能听懂中文，至于写作，还差得远。</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>When I first came to China, I couldn't understand or speak clearly — as for writing and reading, those were even further out of reach.</t>
+          <t>I can understand Chinese — as for writing, I still have a long way to go.</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>新产品已经开始生产了，至于销售时间和价格，现在还不能确定。</t>
+          <t>产品已经投产了，至于价格，还没确定。</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>The new product has already gone into production; as for the launch date and pricing, those haven't been confirmed yet.</t>
+          <t>The product has already gone into production; as for the price, it hasn't been confirmed yet.</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -26567,12 +26567,12 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>假如去那家公司工作能为你提供更多的发展空间，那倒也是个不错的选择。</t>
+          <t>去那家公司能有更多发展空间，那倒也是个好选择。</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>If working at that company would give you more room to grow, that's actually not a bad choice.</t>
+          <t>If that company gives you more room to grow, that's actually not a bad choice.</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -27759,12 +27759,12 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>文章虽短，读后却使人充满力量。</t>
+          <t>虽然很累，她也坚持来上课了。</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>Though the piece is short, it leaves the reader feeling full of strength.</t>
+          <t>Although she was very tired, she still insisted on coming to class.</t>
         </is>
       </c>
     </row>
@@ -28059,12 +28059,12 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>当地政府计划调整地铁的发车时间，以便更多的乘客能够乘坐公共交通。</t>
+          <t>政府调整了地铁发车时间，以便更多乘客能乘坐公共交通。</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>The local government plans to adjust the metro schedule so that more passengers can use public transport.</t>
+          <t>The government adjusted the metro schedule so that more passengers can use public transport.</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
